--- a/data/trending_integrated_20261008_15.xlsx
+++ b/data/trending_integrated_20261008_15.xlsx
@@ -584,7 +584,7 @@
         <v>45</v>
       </c>
       <c r="G2" t="n">
-        <v>240</v>
+        <v>242</v>
       </c>
       <c r="H2" t="n">
         <v>0.2</v>
@@ -610,7 +610,7 @@
         <v>0.65</v>
       </c>
       <c r="O2" t="n">
-        <v>32732225010</v>
+        <v>32796145310</v>
       </c>
       <c r="P2" t="n">
         <v>6310</v>
@@ -659,24 +659,24 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>11480</v>
+        <v>11520</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>'+16.19%</t>
+          <t>'+16.60%</t>
         </is>
       </c>
       <c r="D3" t="n">
         <v>0.04</v>
       </c>
       <c r="E3" t="n">
-        <v>73</v>
+        <v>74</v>
       </c>
       <c r="F3" t="n">
         <v>39</v>
       </c>
       <c r="G3" t="n">
-        <v>297</v>
+        <v>306</v>
       </c>
       <c r="H3" t="n">
         <v>37.45</v>
@@ -702,7 +702,7 @@
         <v>37.41</v>
       </c>
       <c r="O3" t="n">
-        <v>69091987760</v>
+        <v>70118757660</v>
       </c>
       <c r="P3" t="n">
         <v>19150</v>
@@ -751,11 +751,11 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>13780</v>
+        <v>13950</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>'+14.93%</t>
+          <t>'+16.35%</t>
         </is>
       </c>
       <c r="D4" t="n">
@@ -768,7 +768,7 @@
         <v>56</v>
       </c>
       <c r="G4" t="n">
-        <v>202</v>
+        <v>203</v>
       </c>
       <c r="H4" t="n">
         <v>4.43</v>
@@ -794,7 +794,7 @@
         <v>4.66</v>
       </c>
       <c r="O4" t="n">
-        <v>58474242080</v>
+        <v>58944934500</v>
       </c>
       <c r="P4" t="n">
         <v>14980</v>
@@ -839,31 +839,31 @@
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>덕산넵코어스</t>
+          <t>HLB제약</t>
         </is>
       </c>
       <c r="B5" t="n">
-        <v>14460</v>
+        <v>13120</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>'+4.86%</t>
+          <t>'+4.38%</t>
         </is>
       </c>
       <c r="D5" t="n">
-        <v>-0.15</v>
+        <v>-0.8100000000000001</v>
       </c>
       <c r="E5" t="n">
-        <v>648</v>
+        <v>134</v>
       </c>
       <c r="F5" t="n">
-        <v>266</v>
+        <v>74</v>
       </c>
       <c r="G5" t="n">
-        <v>1656</v>
+        <v>288</v>
       </c>
       <c r="H5" t="n">
-        <v>0.09</v>
+        <v>1.07</v>
       </c>
       <c r="I5" t="inlineStr">
         <is>
@@ -871,38 +871,38 @@
         </is>
       </c>
       <c r="J5" t="n">
-        <v>13790</v>
+        <v>12570</v>
       </c>
       <c r="K5" t="n">
-        <v>13410</v>
+        <v>12970</v>
       </c>
       <c r="L5" t="n">
-        <v>15960</v>
+        <v>14200</v>
       </c>
       <c r="M5" t="n">
-        <v>11600</v>
+        <v>12500</v>
       </c>
       <c r="N5" t="n">
-        <v>0.24</v>
+        <v>1.88</v>
       </c>
       <c r="O5" t="n">
-        <v>215499364710</v>
+        <v>87318490780</v>
       </c>
       <c r="P5" t="n">
-        <v>28700</v>
+        <v>22250</v>
       </c>
       <c r="Q5" t="n">
-        <v>11600</v>
+        <v>6000</v>
       </c>
       <c r="R5" t="n">
-        <v>-22000</v>
+        <v>-550000</v>
       </c>
       <c r="S5" t="n">
         <v>0</v>
       </c>
       <c r="T5" t="inlineStr">
         <is>
-          <t>국민권익위 접수 사실 언급. 사기 상장 및 무차별 공매도에 대한 불만 제기. 인공위성 교신 성공 관련 내용.</t>
+          <t>HLB 계열사 중 HLB제약만 상승하지 않는 상황과 유증 물량 정리 후 상승 기대감.</t>
         </is>
       </c>
       <c r="U5" t="inlineStr"/>
@@ -911,11 +911,11 @@
       </c>
       <c r="W5" t="inlineStr">
         <is>
-          <t>['사기상장', '공매도', '인공위성']</t>
+          <t>['HLB제약', '유증', '상승기대']</t>
         </is>
       </c>
       <c r="X5" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="Y5" t="inlineStr">
         <is>
@@ -924,7 +924,7 @@
       </c>
       <c r="Z5" t="inlineStr">
         <is>
-          <t>266690</t>
+          <t>047920</t>
         </is>
       </c>
     </row>
@@ -935,11 +935,11 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>37800</v>
+        <v>37600</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>'+4.42%</t>
+          <t>'+3.87%</t>
         </is>
       </c>
       <c r="D6" t="n">
@@ -952,7 +952,7 @@
         <v>64</v>
       </c>
       <c r="G6" t="n">
-        <v>222</v>
+        <v>225</v>
       </c>
       <c r="H6" t="n">
         <v>31.86</v>
@@ -978,7 +978,7 @@
         <v>31.78</v>
       </c>
       <c r="O6" t="n">
-        <v>130818915925</v>
+        <v>131622505450</v>
       </c>
       <c r="P6" t="n">
         <v>45000</v>
@@ -1023,31 +1023,31 @@
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>HLB제약</t>
+          <t>덕산넵코어스</t>
         </is>
       </c>
       <c r="B7" t="n">
-        <v>13070</v>
+        <v>14040</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>'+3.98%</t>
+          <t>'+1.81%</t>
         </is>
       </c>
       <c r="D7" t="n">
-        <v>-0.8100000000000001</v>
+        <v>-0.15</v>
       </c>
       <c r="E7" t="n">
-        <v>131</v>
+        <v>667</v>
       </c>
       <c r="F7" t="n">
-        <v>74</v>
+        <v>267</v>
       </c>
       <c r="G7" t="n">
-        <v>279</v>
+        <v>1684</v>
       </c>
       <c r="H7" t="n">
-        <v>1.07</v>
+        <v>0.09</v>
       </c>
       <c r="I7" t="inlineStr">
         <is>
@@ -1055,51 +1055,51 @@
         </is>
       </c>
       <c r="J7" t="n">
-        <v>12570</v>
+        <v>13790</v>
       </c>
       <c r="K7" t="n">
-        <v>12970</v>
+        <v>13410</v>
       </c>
       <c r="L7" t="n">
-        <v>14200</v>
+        <v>15960</v>
       </c>
       <c r="M7" t="n">
-        <v>12500</v>
+        <v>11600</v>
       </c>
       <c r="N7" t="n">
-        <v>1.88</v>
+        <v>0.24</v>
       </c>
       <c r="O7" t="n">
-        <v>87055157530</v>
+        <v>219149136195</v>
       </c>
       <c r="P7" t="n">
-        <v>22250</v>
+        <v>28700</v>
       </c>
       <c r="Q7" t="n">
-        <v>6000</v>
+        <v>11600</v>
       </c>
       <c r="R7" t="n">
-        <v>-550000</v>
+        <v>-22000</v>
       </c>
       <c r="S7" t="n">
         <v>0</v>
       </c>
       <c r="T7" t="inlineStr">
         <is>
-          <t>HLB 계열사 중 유일하게 부진한 주가 흐름, 유증 물량 정리 및 공매도 관련 언급.</t>
+          <t>덕산넵코어스 관련 국민권익위 조사 요청 및 사기 상장 의혹 제기.</t>
         </is>
       </c>
       <c r="U7" t="inlineStr"/>
       <c r="V7" t="n">
-        <v>0.25</v>
+        <v>0.3</v>
       </c>
       <c r="W7" t="inlineStr">
         <is>
-          <t>['HLB', '유증', '공매도']</t>
+          <t>['덕산넵코어스', '사기상장', '국민권익위']</t>
         </is>
       </c>
       <c r="X7" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="Y7" t="inlineStr">
         <is>
@@ -1108,7 +1108,7 @@
       </c>
       <c r="Z7" t="inlineStr">
         <is>
-          <t>047920</t>
+          <t>266690</t>
         </is>
       </c>
     </row>
@@ -1119,24 +1119,24 @@
         </is>
       </c>
       <c r="B8" t="n">
-        <v>6660</v>
+        <v>6540</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>'+3.10%</t>
+          <t>'+1.24%</t>
         </is>
       </c>
       <c r="D8" t="n">
         <v>-0.31</v>
       </c>
       <c r="E8" t="n">
-        <v>107</v>
+        <v>110</v>
       </c>
       <c r="F8" t="n">
-        <v>53</v>
+        <v>54</v>
       </c>
       <c r="G8" t="n">
-        <v>236</v>
+        <v>238</v>
       </c>
       <c r="H8" t="n">
         <v>0</v>
@@ -1162,7 +1162,7 @@
         <v>0.31</v>
       </c>
       <c r="O8" t="n">
-        <v>21788859240</v>
+        <v>21909812320</v>
       </c>
       <c r="P8" t="n">
         <v>9680</v>
@@ -1222,13 +1222,13 @@
         <v>-0.73</v>
       </c>
       <c r="E9" t="n">
-        <v>365</v>
+        <v>369</v>
       </c>
       <c r="F9" t="n">
-        <v>187</v>
+        <v>189</v>
       </c>
       <c r="G9" t="n">
-        <v>1331</v>
+        <v>1339</v>
       </c>
       <c r="H9" t="n">
         <v>13.39</v>
@@ -1254,7 +1254,7 @@
         <v>14.12</v>
       </c>
       <c r="O9" t="n">
-        <v>36742543700</v>
+        <v>37143474925</v>
       </c>
       <c r="P9" t="n">
         <v>69200</v>
@@ -1303,11 +1303,11 @@
         </is>
       </c>
       <c r="B10" t="n">
-        <v>8220</v>
+        <v>8240</v>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>'-0.36%</t>
+          <t>'-0.12%</t>
         </is>
       </c>
       <c r="D10" t="n">
@@ -1346,7 +1346,7 @@
         <v>26.55</v>
       </c>
       <c r="O10" t="n">
-        <v>19467706900</v>
+        <v>19875448820</v>
       </c>
       <c r="P10" t="n">
         <v>17950</v>
@@ -1395,11 +1395,11 @@
         </is>
       </c>
       <c r="B11" t="n">
-        <v>1701500</v>
+        <v>1700000</v>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>'-1.25%</t>
+          <t>'-1.33%</t>
         </is>
       </c>
       <c r="D11" t="n">
@@ -1409,10 +1409,10 @@
         <v>800</v>
       </c>
       <c r="F11" t="n">
-        <v>455</v>
+        <v>447</v>
       </c>
       <c r="G11" t="n">
-        <v>1664</v>
+        <v>1662</v>
       </c>
       <c r="H11" t="n">
         <v>49.59</v>
@@ -1438,7 +1438,7 @@
         <v>49.71</v>
       </c>
       <c r="O11" t="n">
-        <v>3799727225500</v>
+        <v>3858694532500</v>
       </c>
       <c r="P11" t="n">
         <v>2987000</v>
@@ -1454,16 +1454,16 @@
       </c>
       <c r="T11" t="inlineStr">
         <is>
-          <t>주가 및 국가 상황에 대한 불만 표출, 솔리다임 상장 관련 최태원 회장 해명 요구 및 정치적 이슈 연계.</t>
+          <t>솔리다임 상장 관련 논란과 주가 부양 없는 국내 증시에 대한 불만.</t>
         </is>
       </c>
       <c r="U11" t="inlineStr"/>
       <c r="V11" t="n">
-        <v>0.05</v>
+        <v>0.1</v>
       </c>
       <c r="W11" t="inlineStr">
         <is>
-          <t>['솔리다임', '최태원', '정치 이슈']</t>
+          <t>['솔리다임', '주가조작', '국내증시']</t>
         </is>
       </c>
       <c r="X11" t="n">
@@ -1483,83 +1483,83 @@
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>삼천당제약</t>
+          <t>삼성전자</t>
         </is>
       </c>
       <c r="B12" t="n">
-        <v>237500</v>
+        <v>264500</v>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>'-1.45%</t>
+          <t>'-1.49%</t>
         </is>
       </c>
       <c r="D12" t="n">
-        <v>-0.65</v>
+        <v>0.01</v>
       </c>
       <c r="E12" t="n">
-        <v>137</v>
+        <v>800</v>
       </c>
       <c r="F12" t="n">
-        <v>76</v>
+        <v>544</v>
       </c>
       <c r="G12" t="n">
-        <v>899</v>
+        <v>2472</v>
       </c>
       <c r="H12" t="n">
-        <v>3.47</v>
+        <v>46.38</v>
       </c>
       <c r="I12" t="inlineStr">
         <is>
-          <t>MarketType.KOSDAQ</t>
+          <t>MarketType.KOSPI</t>
         </is>
       </c>
       <c r="J12" t="n">
-        <v>241000</v>
+        <v>268500</v>
       </c>
       <c r="K12" t="n">
-        <v>227000</v>
+        <v>269500</v>
       </c>
       <c r="L12" t="n">
-        <v>239500</v>
+        <v>270000</v>
       </c>
       <c r="M12" t="n">
-        <v>210500</v>
+        <v>263000</v>
       </c>
       <c r="N12" t="n">
-        <v>4.12</v>
+        <v>46.37</v>
       </c>
       <c r="O12" t="n">
-        <v>50728873250</v>
+        <v>4042446557250</v>
       </c>
       <c r="P12" t="n">
-        <v>1233000</v>
+        <v>374500</v>
       </c>
       <c r="Q12" t="n">
-        <v>120000</v>
+        <v>90200</v>
       </c>
       <c r="R12" t="n">
-        <v>6000</v>
+        <v>56000</v>
       </c>
       <c r="S12" t="n">
-        <v>5000</v>
+        <v>-965000</v>
       </c>
       <c r="T12" t="inlineStr">
         <is>
-          <t>연기금 7일째 매수 및 내년 아일리아 영업이익 기대, 공매도 과열 종목 지정 및 릴레이 계약공시 호재.</t>
+          <t>높은 영업이익에도 불구하고 주가 부양 없는 국내 증시 및 주주환원 정책에 대한 비판.</t>
         </is>
       </c>
       <c r="U12" t="inlineStr"/>
       <c r="V12" t="n">
-        <v>0.3</v>
+        <v>0.1</v>
       </c>
       <c r="W12" t="inlineStr">
         <is>
-          <t>['연기금', '아일리아', '계약공시']</t>
+          <t>['영업이익', '주주환원', '국내증시']</t>
         </is>
       </c>
       <c r="X12" t="n">
-        <v>2</v>
+        <v>8</v>
       </c>
       <c r="Y12" t="inlineStr">
         <is>
@@ -1568,90 +1568,90 @@
       </c>
       <c r="Z12" t="inlineStr">
         <is>
-          <t>000250</t>
+          <t>005930</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>삼성전자</t>
+          <t>삼천당제약</t>
         </is>
       </c>
       <c r="B13" t="n">
-        <v>264500</v>
+        <v>236500</v>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>'-1.49%</t>
+          <t>'-1.87%</t>
         </is>
       </c>
       <c r="D13" t="n">
-        <v>0.01</v>
+        <v>-0.65</v>
       </c>
       <c r="E13" t="n">
-        <v>800</v>
+        <v>139</v>
       </c>
       <c r="F13" t="n">
-        <v>548</v>
+        <v>76</v>
       </c>
       <c r="G13" t="n">
-        <v>2428</v>
+        <v>924</v>
       </c>
       <c r="H13" t="n">
-        <v>46.38</v>
+        <v>3.47</v>
       </c>
       <c r="I13" t="inlineStr">
         <is>
-          <t>MarketType.KOSPI</t>
+          <t>MarketType.KOSDAQ</t>
         </is>
       </c>
       <c r="J13" t="n">
-        <v>268500</v>
+        <v>241000</v>
       </c>
       <c r="K13" t="n">
-        <v>269500</v>
+        <v>227000</v>
       </c>
       <c r="L13" t="n">
-        <v>270000</v>
+        <v>241000</v>
       </c>
       <c r="M13" t="n">
-        <v>263000</v>
+        <v>210500</v>
       </c>
       <c r="N13" t="n">
-        <v>46.37</v>
+        <v>4.12</v>
       </c>
       <c r="O13" t="n">
-        <v>3975645928750</v>
+        <v>53935178750</v>
       </c>
       <c r="P13" t="n">
-        <v>374500</v>
+        <v>1233000</v>
       </c>
       <c r="Q13" t="n">
-        <v>90200</v>
+        <v>120000</v>
       </c>
       <c r="R13" t="n">
-        <v>56000</v>
+        <v>6000</v>
       </c>
       <c r="S13" t="n">
-        <v>-965000</v>
+        <v>5000</v>
       </c>
       <c r="T13" t="inlineStr">
         <is>
-          <t>영업이익 세계 최고에도 불구하고 주가 부양책 부재 및 정치적 이슈로 인한 투자 심리 위축.</t>
+          <t>연기금 7일째 매수 및 캐나다 세마 출시 임박, 릴레이 계약 공시 등 긍정적인 뉴스.</t>
         </is>
       </c>
       <c r="U13" t="inlineStr"/>
       <c r="V13" t="n">
-        <v>0.05</v>
+        <v>0.4</v>
       </c>
       <c r="W13" t="inlineStr">
         <is>
-          <t>['영업이익', '주주환원', '주가 부양']</t>
+          <t>['아일리아', '릴레이계약', '공매도금지']</t>
         </is>
       </c>
       <c r="X13" t="n">
-        <v>8</v>
+        <v>2</v>
       </c>
       <c r="Y13" t="inlineStr">
         <is>
@@ -1660,7 +1660,7 @@
       </c>
       <c r="Z13" t="inlineStr">
         <is>
-          <t>005930</t>
+          <t>000250</t>
         </is>
       </c>
     </row>
@@ -1671,24 +1671,24 @@
         </is>
       </c>
       <c r="B14" t="n">
-        <v>18950</v>
+        <v>18970</v>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>'-3.02%</t>
+          <t>'-2.92%</t>
         </is>
       </c>
       <c r="D14" t="n">
         <v>0.01</v>
       </c>
       <c r="E14" t="n">
-        <v>143</v>
+        <v>146</v>
       </c>
       <c r="F14" t="n">
         <v>80</v>
       </c>
       <c r="G14" t="n">
-        <v>402</v>
+        <v>408</v>
       </c>
       <c r="H14" t="n">
         <v>27.68</v>
@@ -1714,7 +1714,7 @@
         <v>27.67</v>
       </c>
       <c r="O14" t="n">
-        <v>49584632080</v>
+        <v>50886974945</v>
       </c>
       <c r="P14" t="n">
         <v>35350</v>
@@ -1730,7 +1730,7 @@
       </c>
       <c r="T14" t="inlineStr">
         <is>
-          <t>증권사 애널리스트들의 추천 및 조선주 폭락 원인에 대한 불신 표출. 5개월간의 주가 하락세와 폐업 가능성 우려.</t>
+          <t>조선주 폭락에 대한 분석과 함께 애널리스트 및 리딩방에 대한 불신 표출.</t>
         </is>
       </c>
       <c r="U14" t="inlineStr"/>
@@ -1739,7 +1739,7 @@
       </c>
       <c r="W14" t="inlineStr">
         <is>
-          <t>['조선주', '주가 하락', '실적']</t>
+          <t>['조선주', '실적', '애널리스트']</t>
         </is>
       </c>
       <c r="X14" t="n">
@@ -1763,24 +1763,24 @@
         </is>
       </c>
       <c r="B15" t="n">
-        <v>16740</v>
+        <v>16690</v>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>'-3.46%</t>
+          <t>'-3.75%</t>
         </is>
       </c>
       <c r="D15" t="n">
         <v>-0.04</v>
       </c>
       <c r="E15" t="n">
-        <v>127</v>
+        <v>128</v>
       </c>
       <c r="F15" t="n">
         <v>60</v>
       </c>
       <c r="G15" t="n">
-        <v>666</v>
+        <v>680</v>
       </c>
       <c r="H15" t="n">
         <v>9.460000000000001</v>
@@ -1806,7 +1806,7 @@
         <v>9.5</v>
       </c>
       <c r="O15" t="n">
-        <v>48085814040</v>
+        <v>49068258915</v>
       </c>
       <c r="P15" t="n">
         <v>40350</v>
@@ -1851,83 +1851,83 @@
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>국제약품</t>
+          <t>대한광통신</t>
         </is>
       </c>
       <c r="B16" t="n">
-        <v>4230</v>
+        <v>16980</v>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>'-4.51%</t>
+          <t>'-5.35%</t>
         </is>
       </c>
       <c r="D16" t="n">
-        <v>1.19</v>
+        <v>-0.95</v>
       </c>
       <c r="E16" t="n">
-        <v>140</v>
+        <v>147</v>
       </c>
       <c r="F16" t="n">
-        <v>89</v>
+        <v>87</v>
       </c>
       <c r="G16" t="n">
-        <v>200</v>
+        <v>600</v>
       </c>
       <c r="H16" t="n">
-        <v>4.46</v>
+        <v>3.97</v>
       </c>
       <c r="I16" t="inlineStr">
         <is>
-          <t>MarketType.KOSPI</t>
+          <t>MarketType.KOSDAQ</t>
         </is>
       </c>
       <c r="J16" t="n">
-        <v>4430</v>
+        <v>17940</v>
       </c>
       <c r="K16" t="n">
-        <v>4650</v>
+        <v>17770</v>
       </c>
       <c r="L16" t="n">
-        <v>4855</v>
+        <v>17940</v>
       </c>
       <c r="M16" t="n">
-        <v>4185</v>
+        <v>16750</v>
       </c>
       <c r="N16" t="n">
-        <v>3.27</v>
+        <v>4.92</v>
       </c>
       <c r="O16" t="n">
-        <v>92087029443</v>
+        <v>102496900160</v>
       </c>
       <c r="P16" t="n">
-        <v>5470</v>
+        <v>31500</v>
       </c>
       <c r="Q16" t="n">
-        <v>2810</v>
+        <v>1272</v>
       </c>
       <c r="R16" t="n">
-        <v>-471000</v>
+        <v>-412000</v>
       </c>
       <c r="S16" t="n">
-        <v>0</v>
+        <v>-70000</v>
       </c>
       <c r="T16" t="inlineStr">
         <is>
-          <t>미국 항생제 회사 주가 폭등 속 전염병 관련 뉴스 언급. 국제약품의 대장주 여부 및 금일 시가 지지 여부에 관심.</t>
+          <t>미국 광통신주 하락 영향 및 외인/기관 쌍매도, 프로그램 매매 불안정성 지적.</t>
         </is>
       </c>
       <c r="U16" t="inlineStr"/>
       <c r="V16" t="n">
-        <v>0.2</v>
+        <v>0.1</v>
       </c>
       <c r="W16" t="inlineStr">
         <is>
-          <t>['항생제', '전염병', '대장주']</t>
+          <t>['광통신', '외인/기관', '프로그램 매매']</t>
         </is>
       </c>
       <c r="X16" t="n">
-        <v>2</v>
+        <v>8</v>
       </c>
       <c r="Y16" t="inlineStr">
         <is>
@@ -1936,130 +1936,130 @@
       </c>
       <c r="Z16" t="inlineStr">
         <is>
-          <t>002720</t>
+          <t>010170</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>대한광통신</t>
+          <t>대한전선</t>
         </is>
       </c>
       <c r="B17" t="n">
-        <v>16980</v>
+        <v>28200</v>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>'-5.35%</t>
+          <t>'-5.37%</t>
         </is>
       </c>
       <c r="D17" t="n">
-        <v>-0.95</v>
+        <v>-0.76</v>
       </c>
       <c r="E17" t="n">
-        <v>145</v>
+        <v>80</v>
       </c>
       <c r="F17" t="n">
-        <v>85</v>
+        <v>56</v>
       </c>
       <c r="G17" t="n">
-        <v>596</v>
+        <v>217</v>
       </c>
       <c r="H17" t="n">
-        <v>3.97</v>
+        <v>10.02</v>
       </c>
       <c r="I17" t="inlineStr">
         <is>
-          <t>MarketType.KOSDAQ</t>
+          <t>MarketType.KOSPI</t>
         </is>
       </c>
       <c r="J17" t="n">
-        <v>17940</v>
+        <v>29800</v>
       </c>
       <c r="K17" t="n">
-        <v>17770</v>
+        <v>29900</v>
       </c>
       <c r="L17" t="n">
-        <v>17940</v>
+        <v>30000</v>
       </c>
       <c r="M17" t="n">
-        <v>16750</v>
+        <v>28050</v>
       </c>
       <c r="N17" t="n">
-        <v>4.92</v>
+        <v>10.78</v>
       </c>
       <c r="O17" t="n">
-        <v>101559313695</v>
+        <v>70524181775</v>
       </c>
       <c r="P17" t="n">
-        <v>31500</v>
+        <v>75900</v>
       </c>
       <c r="Q17" t="n">
-        <v>1272</v>
+        <v>15960</v>
       </c>
       <c r="R17" t="n">
-        <v>-412000</v>
+        <v>-612000</v>
       </c>
       <c r="S17" t="n">
-        <v>-70000</v>
+        <v>1000</v>
       </c>
       <c r="T17" t="inlineStr">
         <is>
-          <t>미국 광통신주 하락 영향 및 외인/기관 쌍매도, 프로그램 매매 불안정성 지적.</t>
+          <t>연이은 주가 하락(-11%) 및 공매도 프로그램 이용 외국인에 대한 비판. 유상증자 및 고점 물량 부담에 대한 우려 제기.</t>
         </is>
       </c>
       <c r="U17" t="inlineStr"/>
       <c r="V17" t="n">
-        <v>0.1</v>
+        <v>0</v>
       </c>
       <c r="W17" t="inlineStr">
         <is>
-          <t>['광통신', '외인/기관', '프로그램 매매']</t>
+          <t>['주가 하락', '공매도', '유상증자']</t>
         </is>
       </c>
       <c r="X17" t="n">
-        <v>8</v>
+        <v>2</v>
       </c>
       <c r="Y17" t="inlineStr">
         <is>
-          <t>활성</t>
+          <t>추적</t>
         </is>
       </c>
       <c r="Z17" t="inlineStr">
         <is>
-          <t>010170</t>
+          <t>001440</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>대한전선</t>
+          <t>국제약품</t>
         </is>
       </c>
       <c r="B18" t="n">
-        <v>28150</v>
+        <v>4175</v>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>'-5.54%</t>
+          <t>'-5.76%</t>
         </is>
       </c>
       <c r="D18" t="n">
-        <v>-0.76</v>
+        <v>1.19</v>
       </c>
       <c r="E18" t="n">
-        <v>80</v>
+        <v>142</v>
       </c>
       <c r="F18" t="n">
-        <v>56</v>
+        <v>90</v>
       </c>
       <c r="G18" t="n">
-        <v>222</v>
+        <v>204</v>
       </c>
       <c r="H18" t="n">
-        <v>10.02</v>
+        <v>4.46</v>
       </c>
       <c r="I18" t="inlineStr">
         <is>
@@ -2067,47 +2067,47 @@
         </is>
       </c>
       <c r="J18" t="n">
-        <v>29800</v>
+        <v>4430</v>
       </c>
       <c r="K18" t="n">
-        <v>29900</v>
+        <v>4650</v>
       </c>
       <c r="L18" t="n">
-        <v>30000</v>
+        <v>4855</v>
       </c>
       <c r="M18" t="n">
-        <v>28050</v>
+        <v>4160</v>
       </c>
       <c r="N18" t="n">
-        <v>10.78</v>
+        <v>3.27</v>
       </c>
       <c r="O18" t="n">
-        <v>69437127100</v>
+        <v>92701613307</v>
       </c>
       <c r="P18" t="n">
-        <v>75900</v>
+        <v>5470</v>
       </c>
       <c r="Q18" t="n">
-        <v>15960</v>
+        <v>2810</v>
       </c>
       <c r="R18" t="n">
-        <v>-612000</v>
+        <v>-471000</v>
       </c>
       <c r="S18" t="n">
-        <v>1000</v>
+        <v>0</v>
       </c>
       <c r="T18" t="inlineStr">
         <is>
-          <t>연이은 주가 하락(-11%) 및 공매도 프로그램 이용 외국인에 대한 비판. 유상증자 및 고점 물량 부담에 대한 우려 제기.</t>
+          <t>미국 항생제 보유 회사 주가 급등 및 WHO의 러시아 폐렴 관련 상황 파악 지연 소식.</t>
         </is>
       </c>
       <c r="U18" t="inlineStr"/>
       <c r="V18" t="n">
-        <v>0</v>
+        <v>0.2</v>
       </c>
       <c r="W18" t="inlineStr">
         <is>
-          <t>['주가 하락', '공매도', '유상증자']</t>
+          <t>['항생제', '전염병', 'WHO']</t>
         </is>
       </c>
       <c r="X18" t="n">
@@ -2115,12 +2115,12 @@
       </c>
       <c r="Y18" t="inlineStr">
         <is>
-          <t>추적</t>
+          <t>활성</t>
         </is>
       </c>
       <c r="Z18" t="inlineStr">
         <is>
-          <t>001440</t>
+          <t>002720</t>
         </is>
       </c>
     </row>
@@ -2131,24 +2131,24 @@
         </is>
       </c>
       <c r="B19" t="n">
-        <v>75400</v>
+        <v>75200</v>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>'-6.34%</t>
+          <t>'-6.58%</t>
         </is>
       </c>
       <c r="D19" t="n">
         <v>-0.1</v>
       </c>
       <c r="E19" t="n">
-        <v>468</v>
+        <v>476</v>
       </c>
       <c r="F19" t="n">
-        <v>279</v>
+        <v>278</v>
       </c>
       <c r="G19" t="n">
-        <v>1471</v>
+        <v>1487</v>
       </c>
       <c r="H19" t="n">
         <v>22.49</v>
@@ -2174,7 +2174,7 @@
         <v>22.59</v>
       </c>
       <c r="O19" t="n">
-        <v>243083819100</v>
+        <v>248265002100</v>
       </c>
       <c r="P19" t="n">
         <v>139200</v>
@@ -2190,16 +2190,16 @@
       </c>
       <c r="T19" t="inlineStr">
         <is>
-          <t>해외 가스 발전 사업 확정에도 불구하고 정치적 불확실성 및 공매도 이슈로 인한 주가 하락.</t>
+          <t>한미 텍사스 가스 발전 확정 소식과 함께 공매도 및 정치적 요인에 대한 불만 제기.</t>
         </is>
       </c>
       <c r="U19" t="inlineStr"/>
       <c r="V19" t="n">
-        <v>0.1</v>
+        <v>0.3</v>
       </c>
       <c r="W19" t="inlineStr">
         <is>
-          <t>['가스발전', '해외 수주', '공매도']</t>
+          <t>['가스발전', '공매도', '원전']</t>
         </is>
       </c>
       <c r="X19" t="n">
@@ -2223,24 +2223,24 @@
         </is>
       </c>
       <c r="B20" t="n">
-        <v>4855</v>
+        <v>4860</v>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>'-6.81%</t>
+          <t>'-6.72%</t>
         </is>
       </c>
       <c r="D20" t="n">
         <v>-0.07000000000000001</v>
       </c>
       <c r="E20" t="n">
-        <v>96</v>
+        <v>97</v>
       </c>
       <c r="F20" t="n">
         <v>61</v>
       </c>
       <c r="G20" t="n">
-        <v>350</v>
+        <v>360</v>
       </c>
       <c r="H20" t="n">
         <v>4.65</v>
@@ -2266,7 +2266,7 @@
         <v>4.72</v>
       </c>
       <c r="O20" t="n">
-        <v>72247235678</v>
+        <v>72673604847</v>
       </c>
       <c r="P20" t="n">
         <v>8100</v>
@@ -2311,70 +2311,70 @@
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>삼표시멘트</t>
+          <t>한미사이언스</t>
         </is>
       </c>
       <c r="B21" t="n">
-        <v>7260</v>
+        <v>53200</v>
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>'-7.16%</t>
+          <t>'-8.43%</t>
         </is>
       </c>
       <c r="D21" t="n">
-        <v>-2.03</v>
+        <v>0.02</v>
       </c>
       <c r="E21" t="n">
-        <v>233</v>
+        <v>356</v>
       </c>
       <c r="F21" t="n">
-        <v>103</v>
+        <v>164</v>
       </c>
       <c r="G21" t="n">
-        <v>669</v>
+        <v>791</v>
       </c>
       <c r="H21" t="n">
-        <v>3.09</v>
+        <v>1.32</v>
       </c>
       <c r="I21" t="inlineStr">
         <is>
-          <t>MarketType.KOSDAQ</t>
+          <t>MarketType.KOSPI</t>
         </is>
       </c>
       <c r="J21" t="n">
-        <v>7820</v>
+        <v>58100</v>
       </c>
       <c r="K21" t="n">
-        <v>8080</v>
+        <v>63200</v>
       </c>
       <c r="L21" t="n">
-        <v>8510</v>
+        <v>63800</v>
       </c>
       <c r="M21" t="n">
-        <v>6870</v>
+        <v>51700</v>
       </c>
       <c r="N21" t="n">
-        <v>5.12</v>
+        <v>1.3</v>
       </c>
       <c r="O21" t="n">
-        <v>94465557180</v>
+        <v>59131846000</v>
       </c>
       <c r="P21" t="n">
-        <v>23500</v>
+        <v>63800</v>
       </c>
       <c r="Q21" t="n">
-        <v>2890</v>
+        <v>25600</v>
       </c>
       <c r="R21" t="n">
-        <v>-516000</v>
+        <v>-167000</v>
       </c>
       <c r="S21" t="n">
-        <v>0</v>
+        <v>-48000</v>
       </c>
       <c r="T21" t="inlineStr">
         <is>
-          <t>본PF 대주단 구성 중, 성수동 부동산 개발 관련 언급 및 공매도 관련 논란.</t>
+          <t>비만약 승인 재료에도 불구하고 하한가를 기록하는 등 주가 조작 의혹 제기.</t>
         </is>
       </c>
       <c r="U21" t="inlineStr"/>
@@ -2383,11 +2383,11 @@
       </c>
       <c r="W21" t="inlineStr">
         <is>
-          <t>['본PF', '성수동', '공매도']</t>
+          <t>['비만약', '주가조작', '기술수출']</t>
         </is>
       </c>
       <c r="X21" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="Y21" t="inlineStr">
         <is>
@@ -2396,7 +2396,7 @@
       </c>
       <c r="Z21" t="inlineStr">
         <is>
-          <t>038500</t>
+          <t>008930</t>
         </is>
       </c>
     </row>
@@ -2407,24 +2407,24 @@
         </is>
       </c>
       <c r="B22" t="n">
-        <v>15290</v>
+        <v>15270</v>
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>'-8.50%</t>
+          <t>'-8.62%</t>
         </is>
       </c>
       <c r="D22" t="n">
         <v>-1.44</v>
       </c>
       <c r="E22" t="n">
-        <v>62</v>
+        <v>64</v>
       </c>
       <c r="F22" t="n">
-        <v>40</v>
+        <v>41</v>
       </c>
       <c r="G22" t="n">
-        <v>205</v>
+        <v>207</v>
       </c>
       <c r="H22" t="n">
         <v>0.93</v>
@@ -2450,7 +2450,7 @@
         <v>2.37</v>
       </c>
       <c r="O22" t="n">
-        <v>36733126390</v>
+        <v>37001820630</v>
       </c>
       <c r="P22" t="n">
         <v>17590</v>
@@ -2495,83 +2495,83 @@
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>한미사이언스</t>
+          <t>삼표시멘트</t>
         </is>
       </c>
       <c r="B23" t="n">
-        <v>52800</v>
+        <v>7130</v>
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>'-9.12%</t>
+          <t>'-8.82%</t>
         </is>
       </c>
       <c r="D23" t="n">
-        <v>0.02</v>
+        <v>-2.03</v>
       </c>
       <c r="E23" t="n">
-        <v>354</v>
+        <v>239</v>
       </c>
       <c r="F23" t="n">
-        <v>165</v>
+        <v>103</v>
       </c>
       <c r="G23" t="n">
-        <v>772</v>
+        <v>680</v>
       </c>
       <c r="H23" t="n">
-        <v>1.32</v>
+        <v>3.09</v>
       </c>
       <c r="I23" t="inlineStr">
         <is>
-          <t>MarketType.KOSPI</t>
+          <t>MarketType.KOSDAQ</t>
         </is>
       </c>
       <c r="J23" t="n">
-        <v>58100</v>
+        <v>7820</v>
       </c>
       <c r="K23" t="n">
-        <v>63200</v>
+        <v>8080</v>
       </c>
       <c r="L23" t="n">
-        <v>63800</v>
+        <v>8510</v>
       </c>
       <c r="M23" t="n">
-        <v>51700</v>
+        <v>6870</v>
       </c>
       <c r="N23" t="n">
-        <v>1.3</v>
+        <v>5.12</v>
       </c>
       <c r="O23" t="n">
-        <v>58715612600</v>
+        <v>97176788195</v>
       </c>
       <c r="P23" t="n">
-        <v>63800</v>
+        <v>23500</v>
       </c>
       <c r="Q23" t="n">
-        <v>25600</v>
+        <v>2890</v>
       </c>
       <c r="R23" t="n">
-        <v>-167000</v>
+        <v>-516000</v>
       </c>
       <c r="S23" t="n">
-        <v>-48000</v>
+        <v>0</v>
       </c>
       <c r="T23" t="inlineStr">
         <is>
-          <t>비만주 급등과 대비되는 주가 흐름, 기술수출 및 승인 관련 내용에도 하한가 기록, 주가 조작 의혹 제기.</t>
+          <t>삼표시멘트의 본PF 구성 및 부동산 관련 소식과 함께 공매도 및 주가 움직임에 대한 언급.</t>
         </is>
       </c>
       <c r="U23" t="inlineStr"/>
       <c r="V23" t="n">
-        <v>0.05</v>
+        <v>0.3</v>
       </c>
       <c r="W23" t="inlineStr">
         <is>
-          <t>['비만주', '기술수출', '주가 조작']</t>
+          <t>['본PF', '공매도', '부동산']</t>
         </is>
       </c>
       <c r="X23" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="Y23" t="inlineStr">
         <is>
@@ -2580,7 +2580,7 @@
       </c>
       <c r="Z23" t="inlineStr">
         <is>
-          <t>008930</t>
+          <t>038500</t>
         </is>
       </c>
     </row>
@@ -2591,24 +2591,24 @@
         </is>
       </c>
       <c r="B24" t="n">
-        <v>9800</v>
+        <v>9820</v>
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>'-10.99%</t>
+          <t>'-10.81%</t>
         </is>
       </c>
       <c r="D24" t="n">
         <v>0.03</v>
       </c>
       <c r="E24" t="n">
-        <v>122</v>
+        <v>121</v>
       </c>
       <c r="F24" t="n">
-        <v>66</v>
+        <v>65</v>
       </c>
       <c r="G24" t="n">
-        <v>373</v>
+        <v>377</v>
       </c>
       <c r="H24" t="n">
         <v>5.04</v>
@@ -2634,7 +2634,7 @@
         <v>5.01</v>
       </c>
       <c r="O24" t="n">
-        <v>7462593615</v>
+        <v>7652629460</v>
       </c>
       <c r="P24" t="n">
         <v>15900</v>

--- a/data/trending_integrated_20261008_15.xlsx
+++ b/data/trending_integrated_20261008_15.xlsx
@@ -584,7 +584,7 @@
         <v>45</v>
       </c>
       <c r="G2" t="n">
-        <v>242</v>
+        <v>243</v>
       </c>
       <c r="H2" t="n">
         <v>0.2</v>
@@ -610,7 +610,7 @@
         <v>0.65</v>
       </c>
       <c r="O2" t="n">
-        <v>32796145310</v>
+        <v>32836459900</v>
       </c>
       <c r="P2" t="n">
         <v>6310</v>
@@ -659,11 +659,11 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>11520</v>
+        <v>11510</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>'+16.60%</t>
+          <t>'+16.50%</t>
         </is>
       </c>
       <c r="D3" t="n">
@@ -676,7 +676,7 @@
         <v>39</v>
       </c>
       <c r="G3" t="n">
-        <v>306</v>
+        <v>321</v>
       </c>
       <c r="H3" t="n">
         <v>37.45</v>
@@ -702,7 +702,7 @@
         <v>37.41</v>
       </c>
       <c r="O3" t="n">
-        <v>70118757660</v>
+        <v>71139092575</v>
       </c>
       <c r="P3" t="n">
         <v>19150</v>
@@ -751,24 +751,24 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>13950</v>
+        <v>13840</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>'+16.35%</t>
+          <t>'+15.43%</t>
         </is>
       </c>
       <c r="D4" t="n">
         <v>-0.23</v>
       </c>
       <c r="E4" t="n">
-        <v>106</v>
+        <v>108</v>
       </c>
       <c r="F4" t="n">
-        <v>56</v>
+        <v>57</v>
       </c>
       <c r="G4" t="n">
-        <v>203</v>
+        <v>214</v>
       </c>
       <c r="H4" t="n">
         <v>4.43</v>
@@ -794,7 +794,7 @@
         <v>4.66</v>
       </c>
       <c r="O4" t="n">
-        <v>58944934500</v>
+        <v>59575558460</v>
       </c>
       <c r="P4" t="n">
         <v>14980</v>
@@ -843,24 +843,24 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>13120</v>
+        <v>13080</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>'+4.38%</t>
+          <t>'+4.06%</t>
         </is>
       </c>
       <c r="D5" t="n">
         <v>-0.8100000000000001</v>
       </c>
       <c r="E5" t="n">
-        <v>134</v>
+        <v>133</v>
       </c>
       <c r="F5" t="n">
         <v>74</v>
       </c>
       <c r="G5" t="n">
-        <v>288</v>
+        <v>290</v>
       </c>
       <c r="H5" t="n">
         <v>1.07</v>
@@ -886,7 +886,7 @@
         <v>1.88</v>
       </c>
       <c r="O5" t="n">
-        <v>87318490780</v>
+        <v>87703135775</v>
       </c>
       <c r="P5" t="n">
         <v>22250</v>
@@ -902,7 +902,7 @@
       </c>
       <c r="T5" t="inlineStr">
         <is>
-          <t>HLB 계열사 중 HLB제약만 상승하지 않는 상황과 유증 물량 정리 후 상승 기대감.</t>
+          <t>HLB제약의 타 HLB 계열사 대비 부진한 주가 흐름에 대한 아쉬움 표출. 유증 물량 정리 및 공매도 관련 언급.</t>
         </is>
       </c>
       <c r="U5" t="inlineStr"/>
@@ -911,7 +911,7 @@
       </c>
       <c r="W5" t="inlineStr">
         <is>
-          <t>['HLB제약', '유증', '상승기대']</t>
+          <t>['HLB', '유증', '공매도']</t>
         </is>
       </c>
       <c r="X5" t="n">
@@ -935,24 +935,24 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>37600</v>
+        <v>37400</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>'+3.87%</t>
+          <t>'+3.31%</t>
         </is>
       </c>
       <c r="D6" t="n">
         <v>0.08</v>
       </c>
       <c r="E6" t="n">
-        <v>94</v>
+        <v>95</v>
       </c>
       <c r="F6" t="n">
-        <v>64</v>
+        <v>65</v>
       </c>
       <c r="G6" t="n">
-        <v>225</v>
+        <v>229</v>
       </c>
       <c r="H6" t="n">
         <v>31.86</v>
@@ -978,7 +978,7 @@
         <v>31.78</v>
       </c>
       <c r="O6" t="n">
-        <v>131622505450</v>
+        <v>133327145775</v>
       </c>
       <c r="P6" t="n">
         <v>45000</v>
@@ -1027,24 +1027,24 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>14040</v>
+        <v>14050</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>'+1.81%</t>
+          <t>'+1.89%</t>
         </is>
       </c>
       <c r="D7" t="n">
         <v>-0.15</v>
       </c>
       <c r="E7" t="n">
-        <v>667</v>
+        <v>682</v>
       </c>
       <c r="F7" t="n">
-        <v>267</v>
+        <v>269</v>
       </c>
       <c r="G7" t="n">
-        <v>1684</v>
+        <v>1703</v>
       </c>
       <c r="H7" t="n">
         <v>0.09</v>
@@ -1070,7 +1070,7 @@
         <v>0.24</v>
       </c>
       <c r="O7" t="n">
-        <v>219149136195</v>
+        <v>223229271870</v>
       </c>
       <c r="P7" t="n">
         <v>28700</v>
@@ -1115,31 +1115,31 @@
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>본느</t>
+          <t>HLB</t>
         </is>
       </c>
       <c r="B8" t="n">
-        <v>6540</v>
+        <v>45950</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>'+1.24%</t>
+          <t>'+0.11%</t>
         </is>
       </c>
       <c r="D8" t="n">
-        <v>-0.31</v>
+        <v>-0.73</v>
       </c>
       <c r="E8" t="n">
-        <v>110</v>
+        <v>372</v>
       </c>
       <c r="F8" t="n">
-        <v>54</v>
+        <v>190</v>
       </c>
       <c r="G8" t="n">
-        <v>238</v>
+        <v>1358</v>
       </c>
       <c r="H8" t="n">
-        <v>0</v>
+        <v>13.39</v>
       </c>
       <c r="I8" t="inlineStr">
         <is>
@@ -1147,222 +1147,222 @@
         </is>
       </c>
       <c r="J8" t="n">
-        <v>6460</v>
+        <v>45900</v>
       </c>
       <c r="K8" t="n">
-        <v>6930</v>
+        <v>45950</v>
       </c>
       <c r="L8" t="n">
-        <v>8390</v>
+        <v>46500</v>
       </c>
       <c r="M8" t="n">
-        <v>6520</v>
+        <v>45100</v>
       </c>
       <c r="N8" t="n">
-        <v>0.31</v>
+        <v>14.12</v>
       </c>
       <c r="O8" t="n">
-        <v>21909812320</v>
+        <v>37530253575</v>
       </c>
       <c r="P8" t="n">
-        <v>9680</v>
+        <v>69200</v>
       </c>
       <c r="Q8" t="n">
-        <v>371</v>
+        <v>24150</v>
       </c>
       <c r="R8" t="n">
-        <v>-28000</v>
+        <v>-53000</v>
       </c>
       <c r="S8" t="n">
-        <v>0</v>
+        <v>-3000</v>
       </c>
       <c r="T8" t="inlineStr">
         <is>
-          <t>관리종목 해제 및 거래 정상화, 새 주인 확정 가능성 언급. 회사 미래 가치 및 불확실성 해소에 따른 긍정적 전망. 주포의 움직임 및 매물대 돌파 기대감.</t>
+          <t>HLB의 리보세라닙 병용요법 허가 및 FDA 승인 기대감. 무상증자 가능성 언급과 함께 공매도 세력의 발악을 언급하며 주가 상승 전망.</t>
         </is>
       </c>
       <c r="U8" t="inlineStr"/>
       <c r="V8" t="n">
-        <v>0</v>
+        <v>0.5</v>
       </c>
       <c r="W8" t="inlineStr">
         <is>
-          <t>['관리종목 해제', '새 주인', '불확실성 해소']</t>
+          <t>['리보세라닙', 'FDA 승인', '공매도']</t>
         </is>
       </c>
       <c r="X8" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="Y8" t="inlineStr">
         <is>
-          <t>추적</t>
+          <t>활성</t>
         </is>
       </c>
       <c r="Z8" t="inlineStr">
         <is>
-          <t>226340</t>
+          <t>028300</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>HLB</t>
+          <t>LG디스플레이</t>
         </is>
       </c>
       <c r="B9" t="n">
-        <v>45950</v>
+        <v>8220</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>'+0.11%</t>
+          <t>'-0.36%</t>
         </is>
       </c>
       <c r="D9" t="n">
-        <v>-0.73</v>
+        <v>-0.17</v>
       </c>
       <c r="E9" t="n">
-        <v>369</v>
+        <v>93</v>
       </c>
       <c r="F9" t="n">
-        <v>189</v>
+        <v>48</v>
       </c>
       <c r="G9" t="n">
-        <v>1339</v>
+        <v>293</v>
       </c>
       <c r="H9" t="n">
-        <v>13.39</v>
+        <v>26.38</v>
       </c>
       <c r="I9" t="inlineStr">
         <is>
-          <t>MarketType.KOSDAQ</t>
+          <t>MarketType.KOSPI</t>
         </is>
       </c>
       <c r="J9" t="n">
-        <v>45900</v>
+        <v>8250</v>
       </c>
       <c r="K9" t="n">
-        <v>45950</v>
+        <v>8190</v>
       </c>
       <c r="L9" t="n">
-        <v>46500</v>
+        <v>8320</v>
       </c>
       <c r="M9" t="n">
-        <v>45100</v>
+        <v>8090</v>
       </c>
       <c r="N9" t="n">
-        <v>14.12</v>
+        <v>26.55</v>
       </c>
       <c r="O9" t="n">
-        <v>37143474925</v>
+        <v>20624009875</v>
       </c>
       <c r="P9" t="n">
-        <v>69200</v>
+        <v>17950</v>
       </c>
       <c r="Q9" t="n">
-        <v>24150</v>
+        <v>8090</v>
       </c>
       <c r="R9" t="n">
-        <v>-53000</v>
+        <v>-17000</v>
       </c>
       <c r="S9" t="n">
-        <v>-3000</v>
+        <v>149000</v>
       </c>
       <c r="T9" t="inlineStr">
         <is>
-          <t>HLB의 리보세라닙 병용요법 허가 및 FDA 승인 기대감. 무상증자 가능성 언급과 함께 공매도 세력의 발악을 언급하며 주가 상승 전망.</t>
+          <t>과도한 투자 대비 낮은 시가총액에 대한 비판과 경영 방식에 대한 의문. 공매도와 유증에 대한 부정적 인식.</t>
         </is>
       </c>
       <c r="U9" t="inlineStr"/>
       <c r="V9" t="n">
-        <v>0.5</v>
+        <v>0</v>
       </c>
       <c r="W9" t="inlineStr">
         <is>
-          <t>['리보세라닙', 'FDA 승인', '공매도']</t>
+          <t>['시가총액', '공매도', '유증']</t>
         </is>
       </c>
       <c r="X9" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="Y9" t="inlineStr">
         <is>
-          <t>활성</t>
+          <t>추적</t>
         </is>
       </c>
       <c r="Z9" t="inlineStr">
         <is>
-          <t>028300</t>
+          <t>034220</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>LG디스플레이</t>
+          <t>본느</t>
         </is>
       </c>
       <c r="B10" t="n">
-        <v>8240</v>
+        <v>6430</v>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>'-0.12%</t>
+          <t>'-0.46%</t>
         </is>
       </c>
       <c r="D10" t="n">
-        <v>-0.17</v>
+        <v>-0.31</v>
       </c>
       <c r="E10" t="n">
-        <v>90</v>
+        <v>115</v>
       </c>
       <c r="F10" t="n">
-        <v>47</v>
+        <v>57</v>
       </c>
       <c r="G10" t="n">
-        <v>291</v>
+        <v>240</v>
       </c>
       <c r="H10" t="n">
-        <v>26.38</v>
+        <v>0</v>
       </c>
       <c r="I10" t="inlineStr">
         <is>
-          <t>MarketType.KOSPI</t>
+          <t>MarketType.KOSDAQ</t>
         </is>
       </c>
       <c r="J10" t="n">
-        <v>8250</v>
+        <v>6460</v>
       </c>
       <c r="K10" t="n">
-        <v>8190</v>
+        <v>6930</v>
       </c>
       <c r="L10" t="n">
-        <v>8320</v>
+        <v>8390</v>
       </c>
       <c r="M10" t="n">
-        <v>8090</v>
+        <v>6320</v>
       </c>
       <c r="N10" t="n">
-        <v>26.55</v>
+        <v>0.31</v>
       </c>
       <c r="O10" t="n">
-        <v>19875448820</v>
+        <v>22223988240</v>
       </c>
       <c r="P10" t="n">
-        <v>17950</v>
+        <v>9680</v>
       </c>
       <c r="Q10" t="n">
-        <v>8090</v>
+        <v>371</v>
       </c>
       <c r="R10" t="n">
-        <v>-17000</v>
+        <v>-28000</v>
       </c>
       <c r="S10" t="n">
-        <v>149000</v>
+        <v>0</v>
       </c>
       <c r="T10" t="inlineStr">
         <is>
-          <t>과도한 투자 대비 낮은 시가총액에 대한 비판과 경영 방식에 대한 의문. 공매도와 유증에 대한 부정적 인식.</t>
+          <t>관리종목 해제 및 거래 정상화, 새 주인 확정 가능성 언급. 회사 미래 가치 및 불확실성 해소에 따른 긍정적 전망. 주포의 움직임 및 매물대 돌파 기대감.</t>
         </is>
       </c>
       <c r="U10" t="inlineStr"/>
@@ -1371,7 +1371,7 @@
       </c>
       <c r="W10" t="inlineStr">
         <is>
-          <t>['시가총액', '공매도', '유증']</t>
+          <t>['관리종목 해제', '새 주인', '불확실성 해소']</t>
         </is>
       </c>
       <c r="X10" t="n">
@@ -1384,90 +1384,90 @@
       </c>
       <c r="Z10" t="inlineStr">
         <is>
-          <t>034220</t>
+          <t>226340</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>SK하이닉스</t>
+          <t>삼천당제약</t>
         </is>
       </c>
       <c r="B11" t="n">
-        <v>1700000</v>
+        <v>239500</v>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>'-1.33%</t>
+          <t>'-0.62%</t>
         </is>
       </c>
       <c r="D11" t="n">
-        <v>-0.12</v>
+        <v>-0.65</v>
       </c>
       <c r="E11" t="n">
-        <v>800</v>
+        <v>142</v>
       </c>
       <c r="F11" t="n">
-        <v>447</v>
+        <v>76</v>
       </c>
       <c r="G11" t="n">
-        <v>1662</v>
+        <v>948</v>
       </c>
       <c r="H11" t="n">
-        <v>49.59</v>
+        <v>3.47</v>
       </c>
       <c r="I11" t="inlineStr">
         <is>
-          <t>MarketType.KOSPI</t>
+          <t>MarketType.KOSDAQ</t>
         </is>
       </c>
       <c r="J11" t="n">
-        <v>1723000</v>
+        <v>241000</v>
       </c>
       <c r="K11" t="n">
-        <v>1722000</v>
+        <v>227000</v>
       </c>
       <c r="L11" t="n">
-        <v>1759000</v>
+        <v>242500</v>
       </c>
       <c r="M11" t="n">
-        <v>1692000</v>
+        <v>210500</v>
       </c>
       <c r="N11" t="n">
-        <v>49.71</v>
+        <v>4.12</v>
       </c>
       <c r="O11" t="n">
-        <v>3858694532500</v>
+        <v>55806422750</v>
       </c>
       <c r="P11" t="n">
-        <v>2987000</v>
+        <v>1233000</v>
       </c>
       <c r="Q11" t="n">
-        <v>403000</v>
+        <v>120000</v>
       </c>
       <c r="R11" t="n">
-        <v>17000</v>
+        <v>6000</v>
       </c>
       <c r="S11" t="n">
-        <v>-84000</v>
+        <v>5000</v>
       </c>
       <c r="T11" t="inlineStr">
         <is>
-          <t>솔리다임 상장 관련 논란과 주가 부양 없는 국내 증시에 대한 불만.</t>
+          <t>연기금 7일째 매수 및 캐나다 세마 출시 임박, 릴레이 계약 공시 등 긍정적인 뉴스.</t>
         </is>
       </c>
       <c r="U11" t="inlineStr"/>
       <c r="V11" t="n">
-        <v>0.1</v>
+        <v>0.4</v>
       </c>
       <c r="W11" t="inlineStr">
         <is>
-          <t>['솔리다임', '주가조작', '국내증시']</t>
+          <t>['아일리아', '릴레이계약', '공매도금지']</t>
         </is>
       </c>
       <c r="X11" t="n">
-        <v>8</v>
+        <v>2</v>
       </c>
       <c r="Y11" t="inlineStr">
         <is>
@@ -1476,7 +1476,7 @@
       </c>
       <c r="Z11" t="inlineStr">
         <is>
-          <t>000660</t>
+          <t>000250</t>
         </is>
       </c>
     </row>
@@ -1501,10 +1501,10 @@
         <v>800</v>
       </c>
       <c r="F12" t="n">
-        <v>544</v>
+        <v>552</v>
       </c>
       <c r="G12" t="n">
-        <v>2472</v>
+        <v>2447</v>
       </c>
       <c r="H12" t="n">
         <v>46.38</v>
@@ -1530,7 +1530,7 @@
         <v>46.37</v>
       </c>
       <c r="O12" t="n">
-        <v>4042446557250</v>
+        <v>4141523327500</v>
       </c>
       <c r="P12" t="n">
         <v>374500</v>
@@ -1546,7 +1546,7 @@
       </c>
       <c r="T12" t="inlineStr">
         <is>
-          <t>높은 영업이익에도 불구하고 주가 부양 없는 국내 증시 및 주주환원 정책에 대한 비판.</t>
+          <t>삼성전자 역대급 영업이익에도 불구하고 주주환원 부족 및 주가 부양 부재에 대한 불만 고조. 국내 증시 전반에 대한 부정적 인식.</t>
         </is>
       </c>
       <c r="U12" t="inlineStr"/>
@@ -1555,7 +1555,7 @@
       </c>
       <c r="W12" t="inlineStr">
         <is>
-          <t>['영업이익', '주주환원', '국내증시']</t>
+          <t>['영업이익', '주주환원', '국내 증시']</t>
         </is>
       </c>
       <c r="X12" t="n">
@@ -1575,83 +1575,83 @@
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>삼천당제약</t>
+          <t>SK하이닉스</t>
         </is>
       </c>
       <c r="B13" t="n">
-        <v>236500</v>
+        <v>1697000</v>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>'-1.87%</t>
+          <t>'-1.51%</t>
         </is>
       </c>
       <c r="D13" t="n">
-        <v>-0.65</v>
+        <v>-0.12</v>
       </c>
       <c r="E13" t="n">
-        <v>139</v>
+        <v>800</v>
       </c>
       <c r="F13" t="n">
-        <v>76</v>
+        <v>447</v>
       </c>
       <c r="G13" t="n">
-        <v>924</v>
+        <v>1670</v>
       </c>
       <c r="H13" t="n">
-        <v>3.47</v>
+        <v>49.59</v>
       </c>
       <c r="I13" t="inlineStr">
         <is>
-          <t>MarketType.KOSDAQ</t>
+          <t>MarketType.KOSPI</t>
         </is>
       </c>
       <c r="J13" t="n">
-        <v>241000</v>
+        <v>1723000</v>
       </c>
       <c r="K13" t="n">
-        <v>227000</v>
+        <v>1722000</v>
       </c>
       <c r="L13" t="n">
-        <v>241000</v>
+        <v>1759000</v>
       </c>
       <c r="M13" t="n">
-        <v>210500</v>
+        <v>1692000</v>
       </c>
       <c r="N13" t="n">
-        <v>4.12</v>
+        <v>49.71</v>
       </c>
       <c r="O13" t="n">
-        <v>53935178750</v>
+        <v>3923707669000</v>
       </c>
       <c r="P13" t="n">
-        <v>1233000</v>
+        <v>2987000</v>
       </c>
       <c r="Q13" t="n">
-        <v>120000</v>
+        <v>403000</v>
       </c>
       <c r="R13" t="n">
-        <v>6000</v>
+        <v>17000</v>
       </c>
       <c r="S13" t="n">
-        <v>5000</v>
+        <v>-84000</v>
       </c>
       <c r="T13" t="inlineStr">
         <is>
-          <t>연기금 7일째 매수 및 캐나다 세마 출시 임박, 릴레이 계약 공시 등 긍정적인 뉴스.</t>
+          <t>SK하이닉스 관련 부정적인 게시글 다수. 주가 조작 의혹 및 정부 정책에 대한 비판. 한국 증시 전반에 대한 불신.</t>
         </is>
       </c>
       <c r="U13" t="inlineStr"/>
       <c r="V13" t="n">
-        <v>0.4</v>
+        <v>0.1</v>
       </c>
       <c r="W13" t="inlineStr">
         <is>
-          <t>['아일리아', '릴레이계약', '공매도금지']</t>
+          <t>['주가 조작', '정부 정책', '한국 증시']</t>
         </is>
       </c>
       <c r="X13" t="n">
-        <v>2</v>
+        <v>8</v>
       </c>
       <c r="Y13" t="inlineStr">
         <is>
@@ -1660,7 +1660,7 @@
       </c>
       <c r="Z13" t="inlineStr">
         <is>
-          <t>000250</t>
+          <t>000660</t>
         </is>
       </c>
     </row>
@@ -1671,24 +1671,24 @@
         </is>
       </c>
       <c r="B14" t="n">
-        <v>18970</v>
+        <v>18950</v>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>'-2.92%</t>
+          <t>'-3.02%</t>
         </is>
       </c>
       <c r="D14" t="n">
         <v>0.01</v>
       </c>
       <c r="E14" t="n">
-        <v>146</v>
+        <v>151</v>
       </c>
       <c r="F14" t="n">
-        <v>80</v>
+        <v>82</v>
       </c>
       <c r="G14" t="n">
-        <v>408</v>
+        <v>434</v>
       </c>
       <c r="H14" t="n">
         <v>27.68</v>
@@ -1714,7 +1714,7 @@
         <v>27.67</v>
       </c>
       <c r="O14" t="n">
-        <v>50886974945</v>
+        <v>52205842790</v>
       </c>
       <c r="P14" t="n">
         <v>35350</v>
@@ -1730,16 +1730,16 @@
       </c>
       <c r="T14" t="inlineStr">
         <is>
-          <t>조선주 폭락에 대한 분석과 함께 애널리스트 및 리딩방에 대한 불신 표출.</t>
+          <t>삼성중공업 실적 전망에 대한 부정적인 의견과 목표가 하향 소식. 조선주 전반의 하락세 및 주가 부양 부재에 대한 불만.</t>
         </is>
       </c>
       <c r="U14" t="inlineStr"/>
       <c r="V14" t="n">
-        <v>0.2</v>
+        <v>0.1</v>
       </c>
       <c r="W14" t="inlineStr">
         <is>
-          <t>['조선주', '실적', '애널리스트']</t>
+          <t>['실적', '조선주', '목표가']</t>
         </is>
       </c>
       <c r="X14" t="n">
@@ -1759,79 +1759,79 @@
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>대우건설</t>
+          <t>대한광통신</t>
         </is>
       </c>
       <c r="B15" t="n">
-        <v>16690</v>
+        <v>16970</v>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>'-3.75%</t>
+          <t>'-5.41%</t>
         </is>
       </c>
       <c r="D15" t="n">
-        <v>-0.04</v>
+        <v>-0.95</v>
       </c>
       <c r="E15" t="n">
-        <v>128</v>
+        <v>148</v>
       </c>
       <c r="F15" t="n">
-        <v>60</v>
+        <v>86</v>
       </c>
       <c r="G15" t="n">
-        <v>680</v>
+        <v>601</v>
       </c>
       <c r="H15" t="n">
-        <v>9.460000000000001</v>
+        <v>3.97</v>
       </c>
       <c r="I15" t="inlineStr">
         <is>
-          <t>MarketType.KOSPI</t>
+          <t>MarketType.KOSDAQ</t>
         </is>
       </c>
       <c r="J15" t="n">
-        <v>17340</v>
+        <v>17940</v>
       </c>
       <c r="K15" t="n">
-        <v>17190</v>
+        <v>17770</v>
       </c>
       <c r="L15" t="n">
-        <v>17220</v>
+        <v>17940</v>
       </c>
       <c r="M15" t="n">
-        <v>16660</v>
+        <v>16750</v>
       </c>
       <c r="N15" t="n">
-        <v>9.5</v>
+        <v>4.92</v>
       </c>
       <c r="O15" t="n">
-        <v>49068258915</v>
+        <v>103559887120</v>
       </c>
       <c r="P15" t="n">
-        <v>40350</v>
+        <v>31500</v>
       </c>
       <c r="Q15" t="n">
-        <v>3320</v>
+        <v>1272</v>
       </c>
       <c r="R15" t="n">
-        <v>-58000</v>
+        <v>-412000</v>
       </c>
       <c r="S15" t="n">
-        <v>-36000</v>
+        <v>-70000</v>
       </c>
       <c r="T15" t="inlineStr">
         <is>
-          <t>연기금 및 자산운용사의 매매 동향 및 공매도 과열 종목 지정 가능성 언급, 주가 조작 및 지속 성장성 의문 제기.</t>
+          <t>미국 광통신주 하락 영향 및 외인/기관 쌍매도, 프로그램 매매 불안정성 지적.</t>
         </is>
       </c>
       <c r="U15" t="inlineStr"/>
       <c r="V15" t="n">
-        <v>0.15</v>
+        <v>0.1</v>
       </c>
       <c r="W15" t="inlineStr">
         <is>
-          <t>['연기금', '공매도', '주가 조작']</t>
+          <t>['광통신', '외인/기관', '프로그램 매매']</t>
         </is>
       </c>
       <c r="X15" t="n">
@@ -1844,130 +1844,130 @@
       </c>
       <c r="Z15" t="inlineStr">
         <is>
-          <t>047040</t>
+          <t>010170</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>대한광통신</t>
+          <t>대한전선</t>
         </is>
       </c>
       <c r="B16" t="n">
-        <v>16980</v>
+        <v>28075</v>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>'-5.35%</t>
+          <t>'-5.79%</t>
         </is>
       </c>
       <c r="D16" t="n">
-        <v>-0.95</v>
+        <v>-0.76</v>
       </c>
       <c r="E16" t="n">
-        <v>147</v>
+        <v>82</v>
       </c>
       <c r="F16" t="n">
-        <v>87</v>
+        <v>57</v>
       </c>
       <c r="G16" t="n">
-        <v>600</v>
+        <v>223</v>
       </c>
       <c r="H16" t="n">
-        <v>3.97</v>
+        <v>10.02</v>
       </c>
       <c r="I16" t="inlineStr">
         <is>
-          <t>MarketType.KOSDAQ</t>
+          <t>MarketType.KOSPI</t>
         </is>
       </c>
       <c r="J16" t="n">
-        <v>17940</v>
+        <v>29800</v>
       </c>
       <c r="K16" t="n">
-        <v>17770</v>
+        <v>29900</v>
       </c>
       <c r="L16" t="n">
-        <v>17940</v>
+        <v>30000</v>
       </c>
       <c r="M16" t="n">
-        <v>16750</v>
+        <v>28050</v>
       </c>
       <c r="N16" t="n">
-        <v>4.92</v>
+        <v>10.78</v>
       </c>
       <c r="O16" t="n">
-        <v>102496900160</v>
+        <v>73534592700</v>
       </c>
       <c r="P16" t="n">
-        <v>31500</v>
+        <v>75900</v>
       </c>
       <c r="Q16" t="n">
-        <v>1272</v>
+        <v>15960</v>
       </c>
       <c r="R16" t="n">
-        <v>-412000</v>
+        <v>-612000</v>
       </c>
       <c r="S16" t="n">
-        <v>-70000</v>
+        <v>1000</v>
       </c>
       <c r="T16" t="inlineStr">
         <is>
-          <t>미국 광통신주 하락 영향 및 외인/기관 쌍매도, 프로그램 매매 불안정성 지적.</t>
+          <t>연이은 주가 하락(-11%) 및 공매도 프로그램 이용 외국인에 대한 비판. 유상증자 및 고점 물량 부담에 대한 우려 제기.</t>
         </is>
       </c>
       <c r="U16" t="inlineStr"/>
       <c r="V16" t="n">
-        <v>0.1</v>
+        <v>0</v>
       </c>
       <c r="W16" t="inlineStr">
         <is>
-          <t>['광통신', '외인/기관', '프로그램 매매']</t>
+          <t>['주가 하락', '공매도', '유상증자']</t>
         </is>
       </c>
       <c r="X16" t="n">
-        <v>8</v>
+        <v>2</v>
       </c>
       <c r="Y16" t="inlineStr">
         <is>
-          <t>활성</t>
+          <t>추적</t>
         </is>
       </c>
       <c r="Z16" t="inlineStr">
         <is>
-          <t>010170</t>
+          <t>001440</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>대한전선</t>
+          <t>국제약품</t>
         </is>
       </c>
       <c r="B17" t="n">
-        <v>28200</v>
+        <v>4170</v>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>'-5.37%</t>
+          <t>'-5.87%</t>
         </is>
       </c>
       <c r="D17" t="n">
-        <v>-0.76</v>
+        <v>1.19</v>
       </c>
       <c r="E17" t="n">
-        <v>80</v>
+        <v>142</v>
       </c>
       <c r="F17" t="n">
-        <v>56</v>
+        <v>90</v>
       </c>
       <c r="G17" t="n">
-        <v>217</v>
+        <v>210</v>
       </c>
       <c r="H17" t="n">
-        <v>10.02</v>
+        <v>4.46</v>
       </c>
       <c r="I17" t="inlineStr">
         <is>
@@ -1975,47 +1975,47 @@
         </is>
       </c>
       <c r="J17" t="n">
-        <v>29800</v>
+        <v>4430</v>
       </c>
       <c r="K17" t="n">
-        <v>29900</v>
+        <v>4650</v>
       </c>
       <c r="L17" t="n">
-        <v>30000</v>
+        <v>4855</v>
       </c>
       <c r="M17" t="n">
-        <v>28050</v>
+        <v>4160</v>
       </c>
       <c r="N17" t="n">
-        <v>10.78</v>
+        <v>3.27</v>
       </c>
       <c r="O17" t="n">
-        <v>70524181775</v>
+        <v>93390784816</v>
       </c>
       <c r="P17" t="n">
-        <v>75900</v>
+        <v>5470</v>
       </c>
       <c r="Q17" t="n">
-        <v>15960</v>
+        <v>2810</v>
       </c>
       <c r="R17" t="n">
-        <v>-612000</v>
+        <v>-471000</v>
       </c>
       <c r="S17" t="n">
-        <v>1000</v>
+        <v>0</v>
       </c>
       <c r="T17" t="inlineStr">
         <is>
-          <t>연이은 주가 하락(-11%) 및 공매도 프로그램 이용 외국인에 대한 비판. 유상증자 및 고점 물량 부담에 대한 우려 제기.</t>
+          <t>러시아 전염병 관련 소식으로 국제약품에 대한 기대감 형성. WHO의 상황 파악 지연 및 사망자 발생 소식이 혼재.</t>
         </is>
       </c>
       <c r="U17" t="inlineStr"/>
       <c r="V17" t="n">
-        <v>0</v>
+        <v>0.2</v>
       </c>
       <c r="W17" t="inlineStr">
         <is>
-          <t>['주가 하락', '공매도', '유상증자']</t>
+          <t>['전염병', '러시아', 'WHO']</t>
         </is>
       </c>
       <c r="X17" t="n">
@@ -2023,43 +2023,43 @@
       </c>
       <c r="Y17" t="inlineStr">
         <is>
-          <t>추적</t>
+          <t>활성</t>
         </is>
       </c>
       <c r="Z17" t="inlineStr">
         <is>
-          <t>001440</t>
+          <t>002720</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>국제약품</t>
+          <t>두산에너빌리티</t>
         </is>
       </c>
       <c r="B18" t="n">
-        <v>4175</v>
+        <v>75500</v>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>'-5.76%</t>
+          <t>'-6.21%</t>
         </is>
       </c>
       <c r="D18" t="n">
-        <v>1.19</v>
+        <v>-0.1</v>
       </c>
       <c r="E18" t="n">
-        <v>142</v>
+        <v>484</v>
       </c>
       <c r="F18" t="n">
-        <v>90</v>
+        <v>284</v>
       </c>
       <c r="G18" t="n">
-        <v>204</v>
+        <v>1542</v>
       </c>
       <c r="H18" t="n">
-        <v>4.46</v>
+        <v>22.49</v>
       </c>
       <c r="I18" t="inlineStr">
         <is>
@@ -2067,47 +2067,47 @@
         </is>
       </c>
       <c r="J18" t="n">
-        <v>4430</v>
+        <v>80500</v>
       </c>
       <c r="K18" t="n">
-        <v>4650</v>
+        <v>79600</v>
       </c>
       <c r="L18" t="n">
-        <v>4855</v>
+        <v>79600</v>
       </c>
       <c r="M18" t="n">
-        <v>4160</v>
+        <v>75200</v>
       </c>
       <c r="N18" t="n">
-        <v>3.27</v>
+        <v>22.59</v>
       </c>
       <c r="O18" t="n">
-        <v>92701613307</v>
+        <v>256653035450</v>
       </c>
       <c r="P18" t="n">
-        <v>5470</v>
+        <v>139200</v>
       </c>
       <c r="Q18" t="n">
-        <v>2810</v>
+        <v>57000</v>
       </c>
       <c r="R18" t="n">
-        <v>-471000</v>
+        <v>-650000</v>
       </c>
       <c r="S18" t="n">
-        <v>0</v>
+        <v>-117000</v>
       </c>
       <c r="T18" t="inlineStr">
         <is>
-          <t>미국 항생제 보유 회사 주가 급등 및 WHO의 러시아 폐렴 관련 상황 파악 지연 소식.</t>
+          <t>두산에너빌리티 관련 긍정적인 해외 발전소 건설 및 관세 인하 가능성 언급. 그러나 공매도 및 정부 정책에 대한 불만도 제기.</t>
         </is>
       </c>
       <c r="U18" t="inlineStr"/>
       <c r="V18" t="n">
-        <v>0.2</v>
+        <v>0.1</v>
       </c>
       <c r="W18" t="inlineStr">
         <is>
-          <t>['항생제', '전염병', 'WHO']</t>
+          <t>['가스발전', '원전', '공매도']</t>
         </is>
       </c>
       <c r="X18" t="n">
@@ -2120,38 +2120,38 @@
       </c>
       <c r="Z18" t="inlineStr">
         <is>
-          <t>002720</t>
+          <t>034020</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>두산에너빌리티</t>
+          <t>대우건설</t>
         </is>
       </c>
       <c r="B19" t="n">
-        <v>75200</v>
+        <v>16670</v>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>'-6.58%</t>
+          <t>'-6.30%</t>
         </is>
       </c>
       <c r="D19" t="n">
-        <v>-0.1</v>
+        <v>-0.04</v>
       </c>
       <c r="E19" t="n">
-        <v>476</v>
+        <v>132</v>
       </c>
       <c r="F19" t="n">
-        <v>278</v>
+        <v>60</v>
       </c>
       <c r="G19" t="n">
-        <v>1487</v>
+        <v>705</v>
       </c>
       <c r="H19" t="n">
-        <v>22.49</v>
+        <v>9.460000000000001</v>
       </c>
       <c r="I19" t="inlineStr">
         <is>
@@ -2159,51 +2159,51 @@
         </is>
       </c>
       <c r="J19" t="n">
-        <v>80500</v>
+        <v>17790</v>
       </c>
       <c r="K19" t="n">
-        <v>79600</v>
+        <v>0</v>
       </c>
       <c r="L19" t="n">
-        <v>79600</v>
+        <v>0</v>
       </c>
       <c r="M19" t="n">
-        <v>75200</v>
+        <v>0</v>
       </c>
       <c r="N19" t="n">
-        <v>22.59</v>
+        <v>9.5</v>
       </c>
       <c r="O19" t="n">
-        <v>248265002100</v>
+        <v>50634000000</v>
       </c>
       <c r="P19" t="n">
-        <v>139200</v>
+        <v>0</v>
       </c>
       <c r="Q19" t="n">
-        <v>57000</v>
+        <v>0</v>
       </c>
       <c r="R19" t="n">
-        <v>-650000</v>
+        <v>-58000</v>
       </c>
       <c r="S19" t="n">
-        <v>-117000</v>
+        <v>-36000</v>
       </c>
       <c r="T19" t="inlineStr">
         <is>
-          <t>한미 텍사스 가스 발전 확정 소식과 함께 공매도 및 정치적 요인에 대한 불만 제기.</t>
+          <t>대우건설 주가 조작 및 공매도에 대한 의혹 제기. 주주 호소 및 대차 해지의 중요성 강조. 금융 시장 전반에 대한 불신.</t>
         </is>
       </c>
       <c r="U19" t="inlineStr"/>
       <c r="V19" t="n">
-        <v>0.3</v>
+        <v>0.1</v>
       </c>
       <c r="W19" t="inlineStr">
         <is>
-          <t>['가스발전', '공매도', '원전']</t>
+          <t>['주가 조작', '공매도', '대차 해지']</t>
         </is>
       </c>
       <c r="X19" t="n">
-        <v>2</v>
+        <v>8</v>
       </c>
       <c r="Y19" t="inlineStr">
         <is>
@@ -2212,7 +2212,7 @@
       </c>
       <c r="Z19" t="inlineStr">
         <is>
-          <t>034020</t>
+          <t>047040</t>
         </is>
       </c>
     </row>
@@ -2223,24 +2223,24 @@
         </is>
       </c>
       <c r="B20" t="n">
-        <v>4860</v>
+        <v>4870</v>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>'-6.72%</t>
+          <t>'-6.53%</t>
         </is>
       </c>
       <c r="D20" t="n">
         <v>-0.07000000000000001</v>
       </c>
       <c r="E20" t="n">
-        <v>97</v>
+        <v>98</v>
       </c>
       <c r="F20" t="n">
-        <v>61</v>
+        <v>62</v>
       </c>
       <c r="G20" t="n">
-        <v>360</v>
+        <v>364</v>
       </c>
       <c r="H20" t="n">
         <v>4.65</v>
@@ -2266,7 +2266,7 @@
         <v>4.72</v>
       </c>
       <c r="O20" t="n">
-        <v>72673604847</v>
+        <v>73448248340</v>
       </c>
       <c r="P20" t="n">
         <v>8100</v>
@@ -2311,184 +2311,184 @@
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>한미사이언스</t>
+          <t>라온시큐어</t>
         </is>
       </c>
       <c r="B21" t="n">
-        <v>53200</v>
+        <v>15350</v>
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>'-8.43%</t>
+          <t>'-8.14%</t>
         </is>
       </c>
       <c r="D21" t="n">
-        <v>0.02</v>
+        <v>-1.44</v>
       </c>
       <c r="E21" t="n">
-        <v>356</v>
+        <v>64</v>
       </c>
       <c r="F21" t="n">
-        <v>164</v>
+        <v>41</v>
       </c>
       <c r="G21" t="n">
-        <v>791</v>
+        <v>208</v>
       </c>
       <c r="H21" t="n">
-        <v>1.32</v>
+        <v>0.93</v>
       </c>
       <c r="I21" t="inlineStr">
         <is>
-          <t>MarketType.KOSPI</t>
+          <t>MarketType.KOSDAQ</t>
         </is>
       </c>
       <c r="J21" t="n">
-        <v>58100</v>
+        <v>16710</v>
       </c>
       <c r="K21" t="n">
-        <v>63200</v>
+        <v>16460</v>
       </c>
       <c r="L21" t="n">
-        <v>63800</v>
+        <v>17180</v>
       </c>
       <c r="M21" t="n">
-        <v>51700</v>
+        <v>14820</v>
       </c>
       <c r="N21" t="n">
-        <v>1.3</v>
+        <v>2.37</v>
       </c>
       <c r="O21" t="n">
-        <v>59131846000</v>
+        <v>37513928820</v>
       </c>
       <c r="P21" t="n">
-        <v>63800</v>
+        <v>17590</v>
       </c>
       <c r="Q21" t="n">
-        <v>25600</v>
+        <v>6320</v>
       </c>
       <c r="R21" t="n">
-        <v>-167000</v>
+        <v>10000</v>
       </c>
       <c r="S21" t="n">
-        <v>-48000</v>
+        <v>0</v>
       </c>
       <c r="T21" t="inlineStr">
         <is>
-          <t>비만약 승인 재료에도 불구하고 하한가를 기록하는 등 주가 조작 의혹 제기.</t>
+          <t>KDB생명 해킹 방어 성공 및 AI 사이버보안 협의체 선정 뉴스. SKT와의 협력 기반 역대 고점 돌파 기대.</t>
         </is>
       </c>
       <c r="U21" t="inlineStr"/>
       <c r="V21" t="n">
-        <v>0.2</v>
+        <v>0</v>
       </c>
       <c r="W21" t="inlineStr">
         <is>
-          <t>['비만약', '주가조작', '기술수출']</t>
+          <t>['양자보안', 'AI', '사이버보안']</t>
         </is>
       </c>
       <c r="X21" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="Y21" t="inlineStr">
         <is>
-          <t>활성</t>
+          <t>추적</t>
         </is>
       </c>
       <c r="Z21" t="inlineStr">
         <is>
-          <t>008930</t>
+          <t>042510</t>
         </is>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>라온시큐어</t>
+          <t>한미사이언스</t>
         </is>
       </c>
       <c r="B22" t="n">
-        <v>15270</v>
+        <v>52800</v>
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>'-8.62%</t>
+          <t>'-9.12%</t>
         </is>
       </c>
       <c r="D22" t="n">
-        <v>-1.44</v>
+        <v>0.02</v>
       </c>
       <c r="E22" t="n">
-        <v>64</v>
+        <v>356</v>
       </c>
       <c r="F22" t="n">
-        <v>41</v>
+        <v>164</v>
       </c>
       <c r="G22" t="n">
-        <v>207</v>
+        <v>799</v>
       </c>
       <c r="H22" t="n">
-        <v>0.93</v>
+        <v>1.32</v>
       </c>
       <c r="I22" t="inlineStr">
         <is>
-          <t>MarketType.KOSDAQ</t>
+          <t>MarketType.KOSPI</t>
         </is>
       </c>
       <c r="J22" t="n">
-        <v>16710</v>
+        <v>58100</v>
       </c>
       <c r="K22" t="n">
-        <v>16460</v>
+        <v>63200</v>
       </c>
       <c r="L22" t="n">
-        <v>17180</v>
+        <v>63800</v>
       </c>
       <c r="M22" t="n">
-        <v>14820</v>
+        <v>51700</v>
       </c>
       <c r="N22" t="n">
-        <v>2.37</v>
+        <v>1.3</v>
       </c>
       <c r="O22" t="n">
-        <v>37001820630</v>
+        <v>59764795750</v>
       </c>
       <c r="P22" t="n">
-        <v>17590</v>
+        <v>63800</v>
       </c>
       <c r="Q22" t="n">
-        <v>6320</v>
+        <v>25600</v>
       </c>
       <c r="R22" t="n">
-        <v>10000</v>
+        <v>-167000</v>
       </c>
       <c r="S22" t="n">
-        <v>0</v>
+        <v>-48000</v>
       </c>
       <c r="T22" t="inlineStr">
         <is>
-          <t>KDB생명 해킹 방어 성공 및 AI 사이버보안 협의체 선정 뉴스. SKT와의 협력 기반 역대 고점 돌파 기대.</t>
+          <t>한미사이언스 주가 조작 및 악질적인 주가 부양 행태에 대한 강한 비판. 신약 승인 재료에도 불구하고 하한가 기록.</t>
         </is>
       </c>
       <c r="U22" t="inlineStr"/>
       <c r="V22" t="n">
-        <v>0</v>
+        <v>0.1</v>
       </c>
       <c r="W22" t="inlineStr">
         <is>
-          <t>['양자보안', 'AI', '사이버보안']</t>
+          <t>['주가 조작', '신약', '하한가']</t>
         </is>
       </c>
       <c r="X22" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="Y22" t="inlineStr">
         <is>
-          <t>추적</t>
+          <t>활성</t>
         </is>
       </c>
       <c r="Z22" t="inlineStr">
         <is>
-          <t>042510</t>
+          <t>008930</t>
         </is>
       </c>
     </row>
@@ -2499,24 +2499,24 @@
         </is>
       </c>
       <c r="B23" t="n">
-        <v>7130</v>
+        <v>7020</v>
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>'-8.82%</t>
+          <t>'-10.23%</t>
         </is>
       </c>
       <c r="D23" t="n">
         <v>-2.03</v>
       </c>
       <c r="E23" t="n">
-        <v>239</v>
+        <v>242</v>
       </c>
       <c r="F23" t="n">
-        <v>103</v>
+        <v>104</v>
       </c>
       <c r="G23" t="n">
-        <v>680</v>
+        <v>697</v>
       </c>
       <c r="H23" t="n">
         <v>3.09</v>
@@ -2542,7 +2542,7 @@
         <v>5.12</v>
       </c>
       <c r="O23" t="n">
-        <v>97176788195</v>
+        <v>98326755395</v>
       </c>
       <c r="P23" t="n">
         <v>23500</v>
@@ -2591,24 +2591,24 @@
         </is>
       </c>
       <c r="B24" t="n">
-        <v>9820</v>
+        <v>9780</v>
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>'-10.81%</t>
+          <t>'-11.17%</t>
         </is>
       </c>
       <c r="D24" t="n">
         <v>0.03</v>
       </c>
       <c r="E24" t="n">
-        <v>121</v>
+        <v>124</v>
       </c>
       <c r="F24" t="n">
         <v>65</v>
       </c>
       <c r="G24" t="n">
-        <v>377</v>
+        <v>394</v>
       </c>
       <c r="H24" t="n">
         <v>5.04</v>
@@ -2634,7 +2634,7 @@
         <v>5.01</v>
       </c>
       <c r="O24" t="n">
-        <v>7652629460</v>
+        <v>7756060400</v>
       </c>
       <c r="P24" t="n">
         <v>15900</v>
@@ -2650,7 +2650,7 @@
       </c>
       <c r="T24" t="inlineStr">
         <is>
-          <t>미국 항생제 회사 급등과 대비되는 주가, 케냐 에볼라 확진 소식 및 공포 세일 언급, 자사주 매집량 주목.</t>
+          <t>신풍제약 관련 바이러스 테마주로서의 기대감 형성. 자사주 매집 물량 언급 및 상승 가능성 제시. 일부 매도세에 대한 경계.</t>
         </is>
       </c>
       <c r="U24" t="inlineStr"/>
@@ -2659,7 +2659,7 @@
       </c>
       <c r="W24" t="inlineStr">
         <is>
-          <t>['항생제', '에볼라', '자사주 매집']</t>
+          <t>['바이러스', '자사주', '테마주']</t>
         </is>
       </c>
       <c r="X24" t="n">

--- a/data/trending_integrated_20261008_15.xlsx
+++ b/data/trending_integrated_20261008_15.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:Z24"/>
+  <dimension ref="A1:Z25"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -578,13 +578,13 @@
         <v>-0.45</v>
       </c>
       <c r="E2" t="n">
-        <v>77</v>
+        <v>79</v>
       </c>
       <c r="F2" t="n">
-        <v>45</v>
+        <v>47</v>
       </c>
       <c r="G2" t="n">
-        <v>243</v>
+        <v>244</v>
       </c>
       <c r="H2" t="n">
         <v>0.2</v>
@@ -610,7 +610,7 @@
         <v>0.65</v>
       </c>
       <c r="O2" t="n">
-        <v>32836459900</v>
+        <v>32843779500</v>
       </c>
       <c r="P2" t="n">
         <v>6310</v>
@@ -655,31 +655,31 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>피노</t>
+          <t>동국산업</t>
         </is>
       </c>
       <c r="B3" t="n">
-        <v>11510</v>
+        <v>4710</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>'+16.50%</t>
+          <t>'+22.34%</t>
         </is>
       </c>
       <c r="D3" t="n">
-        <v>0.04</v>
+        <v>-0.08</v>
       </c>
       <c r="E3" t="n">
-        <v>74</v>
+        <v>124</v>
       </c>
       <c r="F3" t="n">
-        <v>39</v>
+        <v>57</v>
       </c>
       <c r="G3" t="n">
-        <v>321</v>
+        <v>179</v>
       </c>
       <c r="H3" t="n">
-        <v>37.45</v>
+        <v>1.47</v>
       </c>
       <c r="I3" t="inlineStr">
         <is>
@@ -687,47 +687,47 @@
         </is>
       </c>
       <c r="J3" t="n">
-        <v>9880</v>
+        <v>3850</v>
       </c>
       <c r="K3" t="n">
-        <v>10030</v>
+        <v>3910</v>
       </c>
       <c r="L3" t="n">
-        <v>11600</v>
+        <v>4905</v>
       </c>
       <c r="M3" t="n">
-        <v>9850</v>
+        <v>3865</v>
       </c>
       <c r="N3" t="n">
-        <v>37.41</v>
+        <v>1.55</v>
       </c>
       <c r="O3" t="n">
-        <v>71139092575</v>
+        <v>94552390770</v>
       </c>
       <c r="P3" t="n">
-        <v>19150</v>
+        <v>4905</v>
       </c>
       <c r="Q3" t="n">
-        <v>3445</v>
+        <v>2125</v>
       </c>
       <c r="R3" t="n">
-        <v>133000</v>
+        <v>-41000</v>
       </c>
       <c r="S3" t="n">
-        <v>508000</v>
+        <v>18000</v>
       </c>
       <c r="T3" t="inlineStr">
         <is>
-          <t>전구체 독점 공급 및 양극재 사업 분할 관련 긍정적 뉴스. 매출 5천억 달성 및 전고점 돌파 기대감으로 주가 상승.</t>
+          <t>동국산업의 급등세 지속 및 상한가 기대감 형성. 주가 상승에 대한 긍정적 전망과 함께 '신고가', '대장' 등의 용어로 상승 모멘텀 강조. 다만, 막판 급락 가능성 언급으로 인한 경계감도 존재.</t>
         </is>
       </c>
       <c r="U3" t="inlineStr"/>
       <c r="V3" t="n">
-        <v>0</v>
+        <v>0.3</v>
       </c>
       <c r="W3" t="inlineStr">
         <is>
-          <t>['전구체', '양극재', '매출']</t>
+          <t>['상한가', '신고가', '주포']</t>
         </is>
       </c>
       <c r="X3" t="n">
@@ -735,43 +735,43 @@
       </c>
       <c r="Y3" t="inlineStr">
         <is>
-          <t>추적</t>
+          <t>활성</t>
         </is>
       </c>
       <c r="Z3" t="inlineStr">
         <is>
-          <t>033790</t>
+          <t>005160</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>비아트론</t>
+          <t>피노</t>
         </is>
       </c>
       <c r="B4" t="n">
-        <v>13840</v>
+        <v>11580</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>'+15.43%</t>
+          <t>'+17.21%</t>
         </is>
       </c>
       <c r="D4" t="n">
-        <v>-0.23</v>
+        <v>0.04</v>
       </c>
       <c r="E4" t="n">
-        <v>108</v>
+        <v>74</v>
       </c>
       <c r="F4" t="n">
-        <v>57</v>
+        <v>39</v>
       </c>
       <c r="G4" t="n">
-        <v>214</v>
+        <v>324</v>
       </c>
       <c r="H4" t="n">
-        <v>4.43</v>
+        <v>37.45</v>
       </c>
       <c r="I4" t="inlineStr">
         <is>
@@ -779,38 +779,38 @@
         </is>
       </c>
       <c r="J4" t="n">
-        <v>11990</v>
+        <v>9880</v>
       </c>
       <c r="K4" t="n">
-        <v>14330</v>
+        <v>10030</v>
       </c>
       <c r="L4" t="n">
-        <v>14980</v>
+        <v>11600</v>
       </c>
       <c r="M4" t="n">
-        <v>13070</v>
+        <v>9850</v>
       </c>
       <c r="N4" t="n">
-        <v>4.66</v>
+        <v>37.41</v>
       </c>
       <c r="O4" t="n">
-        <v>59575558460</v>
+        <v>71919190855</v>
       </c>
       <c r="P4" t="n">
-        <v>14980</v>
+        <v>19150</v>
       </c>
       <c r="Q4" t="n">
-        <v>6500</v>
+        <v>3445</v>
       </c>
       <c r="R4" t="n">
-        <v>-23000</v>
+        <v>133000</v>
       </c>
       <c r="S4" t="n">
-        <v>-39000</v>
+        <v>508000</v>
       </c>
       <c r="T4" t="inlineStr">
         <is>
-          <t>유리기판 공정용 글라스본더 개발 완료 및 삼성전기와의 공동 개발 사실 강조. 대당 50억의 고가 장비로 수천억 매출 발생 가능성 및 향후 BPS, 배당률 비교 우위 분석. 유리기판 신대장주 기대감.</t>
+          <t>전구체 독점 공급 및 양극재 사업 분할 관련 긍정적 뉴스. 매출 5천억 달성 및 전고점 돌파 기대감으로 주가 상승.</t>
         </is>
       </c>
       <c r="U4" t="inlineStr"/>
@@ -819,7 +819,7 @@
       </c>
       <c r="W4" t="inlineStr">
         <is>
-          <t>['글라스본더', '유리기판', '삼성전기']</t>
+          <t>['전구체', '양극재', '매출']</t>
         </is>
       </c>
       <c r="X4" t="n">
@@ -832,38 +832,38 @@
       </c>
       <c r="Z4" t="inlineStr">
         <is>
-          <t>141000</t>
+          <t>033790</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>HLB제약</t>
+          <t>비아트론</t>
         </is>
       </c>
       <c r="B5" t="n">
-        <v>13080</v>
+        <v>13840</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>'+4.06%</t>
+          <t>'+15.43%</t>
         </is>
       </c>
       <c r="D5" t="n">
-        <v>-0.8100000000000001</v>
+        <v>-0.23</v>
       </c>
       <c r="E5" t="n">
-        <v>133</v>
+        <v>107</v>
       </c>
       <c r="F5" t="n">
-        <v>74</v>
+        <v>55</v>
       </c>
       <c r="G5" t="n">
-        <v>290</v>
+        <v>210</v>
       </c>
       <c r="H5" t="n">
-        <v>1.07</v>
+        <v>4.43</v>
       </c>
       <c r="I5" t="inlineStr">
         <is>
@@ -871,91 +871,91 @@
         </is>
       </c>
       <c r="J5" t="n">
-        <v>12570</v>
+        <v>11990</v>
       </c>
       <c r="K5" t="n">
-        <v>12970</v>
+        <v>14330</v>
       </c>
       <c r="L5" t="n">
-        <v>14200</v>
+        <v>14980</v>
       </c>
       <c r="M5" t="n">
-        <v>12500</v>
+        <v>13070</v>
       </c>
       <c r="N5" t="n">
-        <v>1.88</v>
+        <v>4.66</v>
       </c>
       <c r="O5" t="n">
-        <v>87703135775</v>
+        <v>59682084940</v>
       </c>
       <c r="P5" t="n">
-        <v>22250</v>
+        <v>14980</v>
       </c>
       <c r="Q5" t="n">
-        <v>6000</v>
+        <v>6500</v>
       </c>
       <c r="R5" t="n">
-        <v>-550000</v>
+        <v>-23000</v>
       </c>
       <c r="S5" t="n">
-        <v>0</v>
+        <v>-39000</v>
       </c>
       <c r="T5" t="inlineStr">
         <is>
-          <t>HLB제약의 타 HLB 계열사 대비 부진한 주가 흐름에 대한 아쉬움 표출. 유증 물량 정리 및 공매도 관련 언급.</t>
+          <t>유리기판 공정용 글라스본더 개발 완료 및 삼성전기와의 공동 개발 사실 강조. 대당 50억의 고가 장비로 수천억 매출 발생 가능성 및 향후 BPS, 배당률 비교 우위 분석. 유리기판 신대장주 기대감.</t>
         </is>
       </c>
       <c r="U5" t="inlineStr"/>
       <c r="V5" t="n">
-        <v>0.2</v>
+        <v>0</v>
       </c>
       <c r="W5" t="inlineStr">
         <is>
-          <t>['HLB', '유증', '공매도']</t>
+          <t>['글라스본더', '유리기판', '삼성전기']</t>
         </is>
       </c>
       <c r="X5" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="Y5" t="inlineStr">
         <is>
-          <t>활성</t>
+          <t>추적</t>
         </is>
       </c>
       <c r="Z5" t="inlineStr">
         <is>
-          <t>047920</t>
+          <t>141000</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>고영</t>
+          <t>HLB제약</t>
         </is>
       </c>
       <c r="B6" t="n">
-        <v>37400</v>
+        <v>13130</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>'+3.31%</t>
+          <t>'+4.46%</t>
         </is>
       </c>
       <c r="D6" t="n">
-        <v>0.08</v>
+        <v>-0.8100000000000001</v>
       </c>
       <c r="E6" t="n">
-        <v>95</v>
+        <v>134</v>
       </c>
       <c r="F6" t="n">
-        <v>65</v>
+        <v>75</v>
       </c>
       <c r="G6" t="n">
-        <v>229</v>
+        <v>295</v>
       </c>
       <c r="H6" t="n">
-        <v>31.86</v>
+        <v>1.07</v>
       </c>
       <c r="I6" t="inlineStr">
         <is>
@@ -963,91 +963,91 @@
         </is>
       </c>
       <c r="J6" t="n">
-        <v>36200</v>
+        <v>12570</v>
       </c>
       <c r="K6" t="n">
-        <v>36250</v>
+        <v>12970</v>
       </c>
       <c r="L6" t="n">
-        <v>39850</v>
+        <v>14200</v>
       </c>
       <c r="M6" t="n">
-        <v>36000</v>
+        <v>12500</v>
       </c>
       <c r="N6" t="n">
-        <v>31.78</v>
+        <v>1.88</v>
       </c>
       <c r="O6" t="n">
-        <v>133327145775</v>
+        <v>87909683805</v>
       </c>
       <c r="P6" t="n">
-        <v>45000</v>
+        <v>22250</v>
       </c>
       <c r="Q6" t="n">
-        <v>15530</v>
+        <v>6000</v>
       </c>
       <c r="R6" t="n">
-        <v>247000</v>
+        <v>-550000</v>
       </c>
       <c r="S6" t="n">
-        <v>36000</v>
+        <v>0</v>
       </c>
       <c r="T6" t="inlineStr">
         <is>
-          <t>JP모건의 매수세와 기관/외국인 매수 물량이 긍정적. 현재 추세와 하락장 속에서의 강한 버팀목 역할 분석.</t>
+          <t>HLB제약의 타 HLB 계열사 대비 부진한 주가 흐름에 대한 아쉬움 표출. 유증 물량 정리 및 공매도 관련 언급.</t>
         </is>
       </c>
       <c r="U6" t="inlineStr"/>
       <c r="V6" t="n">
-        <v>0</v>
+        <v>0.2</v>
       </c>
       <c r="W6" t="inlineStr">
         <is>
-          <t>['기관 매수', '외국인 매수', '추세']</t>
+          <t>['HLB', '유증', '공매도']</t>
         </is>
       </c>
       <c r="X6" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="Y6" t="inlineStr">
         <is>
-          <t>추적</t>
+          <t>활성</t>
         </is>
       </c>
       <c r="Z6" t="inlineStr">
         <is>
-          <t>098460</t>
+          <t>047920</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>덕산넵코어스</t>
+          <t>고영</t>
         </is>
       </c>
       <c r="B7" t="n">
-        <v>14050</v>
+        <v>37500</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>'+1.89%</t>
+          <t>'+3.59%</t>
         </is>
       </c>
       <c r="D7" t="n">
-        <v>-0.15</v>
+        <v>0.08</v>
       </c>
       <c r="E7" t="n">
-        <v>682</v>
+        <v>96</v>
       </c>
       <c r="F7" t="n">
-        <v>269</v>
+        <v>65</v>
       </c>
       <c r="G7" t="n">
-        <v>1703</v>
+        <v>236</v>
       </c>
       <c r="H7" t="n">
-        <v>0.09</v>
+        <v>31.86</v>
       </c>
       <c r="I7" t="inlineStr">
         <is>
@@ -1055,47 +1055,47 @@
         </is>
       </c>
       <c r="J7" t="n">
-        <v>13790</v>
+        <v>36200</v>
       </c>
       <c r="K7" t="n">
-        <v>13410</v>
+        <v>36250</v>
       </c>
       <c r="L7" t="n">
-        <v>15960</v>
+        <v>39850</v>
       </c>
       <c r="M7" t="n">
-        <v>11600</v>
+        <v>36000</v>
       </c>
       <c r="N7" t="n">
-        <v>0.24</v>
+        <v>31.78</v>
       </c>
       <c r="O7" t="n">
-        <v>223229271870</v>
+        <v>138058033275</v>
       </c>
       <c r="P7" t="n">
-        <v>28700</v>
+        <v>45000</v>
       </c>
       <c r="Q7" t="n">
-        <v>11600</v>
+        <v>15530</v>
       </c>
       <c r="R7" t="n">
-        <v>-22000</v>
+        <v>247000</v>
       </c>
       <c r="S7" t="n">
-        <v>0</v>
+        <v>36000</v>
       </c>
       <c r="T7" t="inlineStr">
         <is>
-          <t>덕산넵코어스 관련 국민권익위 조사 요청 및 사기 상장 의혹 제기.</t>
+          <t>JP모건의 매수세와 기관/외국인 매수 물량이 긍정적. 현재 추세와 하락장 속에서의 강한 버팀목 역할 분석.</t>
         </is>
       </c>
       <c r="U7" t="inlineStr"/>
       <c r="V7" t="n">
-        <v>0.3</v>
+        <v>0</v>
       </c>
       <c r="W7" t="inlineStr">
         <is>
-          <t>['덕산넵코어스', '사기상장', '국민권익위']</t>
+          <t>['기관 매수', '외국인 매수', '추세']</t>
         </is>
       </c>
       <c r="X7" t="n">
@@ -1103,43 +1103,43 @@
       </c>
       <c r="Y7" t="inlineStr">
         <is>
-          <t>활성</t>
+          <t>추적</t>
         </is>
       </c>
       <c r="Z7" t="inlineStr">
         <is>
-          <t>266690</t>
+          <t>098460</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>HLB</t>
+          <t>삼천당제약</t>
         </is>
       </c>
       <c r="B8" t="n">
-        <v>45950</v>
+        <v>243500</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>'+0.11%</t>
+          <t>'+1.04%</t>
         </is>
       </c>
       <c r="D8" t="n">
-        <v>-0.73</v>
+        <v>-0.65</v>
       </c>
       <c r="E8" t="n">
-        <v>372</v>
+        <v>149</v>
       </c>
       <c r="F8" t="n">
-        <v>190</v>
+        <v>81</v>
       </c>
       <c r="G8" t="n">
-        <v>1358</v>
+        <v>989</v>
       </c>
       <c r="H8" t="n">
-        <v>13.39</v>
+        <v>3.47</v>
       </c>
       <c r="I8" t="inlineStr">
         <is>
@@ -1147,38 +1147,38 @@
         </is>
       </c>
       <c r="J8" t="n">
-        <v>45900</v>
+        <v>241000</v>
       </c>
       <c r="K8" t="n">
-        <v>45950</v>
+        <v>227000</v>
       </c>
       <c r="L8" t="n">
-        <v>46500</v>
+        <v>243500</v>
       </c>
       <c r="M8" t="n">
-        <v>45100</v>
+        <v>210500</v>
       </c>
       <c r="N8" t="n">
-        <v>14.12</v>
+        <v>4.12</v>
       </c>
       <c r="O8" t="n">
-        <v>37530253575</v>
+        <v>62120864750</v>
       </c>
       <c r="P8" t="n">
-        <v>69200</v>
+        <v>1233000</v>
       </c>
       <c r="Q8" t="n">
-        <v>24150</v>
+        <v>120000</v>
       </c>
       <c r="R8" t="n">
-        <v>-53000</v>
+        <v>6000</v>
       </c>
       <c r="S8" t="n">
-        <v>-3000</v>
+        <v>5000</v>
       </c>
       <c r="T8" t="inlineStr">
         <is>
-          <t>HLB의 리보세라닙 병용요법 허가 및 FDA 승인 기대감. 무상증자 가능성 언급과 함께 공매도 세력의 발악을 언급하며 주가 상승 전망.</t>
+          <t>삼천당제약의 연기금 매수세 유입 및 4분기 실적 기대감. '아일리아', '릴레이 계약공시' 등 구체적인 사업 내용 언급과 함께 3연상 기대감 표출. 공매도 금지 조치에 따른 수급 개선 전망.</t>
         </is>
       </c>
       <c r="U8" t="inlineStr"/>
@@ -1187,11 +1187,11 @@
       </c>
       <c r="W8" t="inlineStr">
         <is>
-          <t>['리보세라닙', 'FDA 승인', '공매도']</t>
+          <t>['아일리아', '계약공시', '공매도']</t>
         </is>
       </c>
       <c r="X8" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="Y8" t="inlineStr">
         <is>
@@ -1200,86 +1200,86 @@
       </c>
       <c r="Z8" t="inlineStr">
         <is>
-          <t>028300</t>
+          <t>000250</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>LG디스플레이</t>
+          <t>덕산넵코어스</t>
         </is>
       </c>
       <c r="B9" t="n">
-        <v>8220</v>
+        <v>13910</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>'-0.36%</t>
+          <t>'+0.87%</t>
         </is>
       </c>
       <c r="D9" t="n">
-        <v>-0.17</v>
+        <v>-0.15</v>
       </c>
       <c r="E9" t="n">
-        <v>93</v>
+        <v>693</v>
       </c>
       <c r="F9" t="n">
-        <v>48</v>
+        <v>276</v>
       </c>
       <c r="G9" t="n">
-        <v>293</v>
+        <v>1718</v>
       </c>
       <c r="H9" t="n">
-        <v>26.38</v>
+        <v>0.09</v>
       </c>
       <c r="I9" t="inlineStr">
         <is>
-          <t>MarketType.KOSPI</t>
+          <t>MarketType.KOSDAQ</t>
         </is>
       </c>
       <c r="J9" t="n">
-        <v>8250</v>
+        <v>13790</v>
       </c>
       <c r="K9" t="n">
-        <v>8190</v>
+        <v>13410</v>
       </c>
       <c r="L9" t="n">
-        <v>8320</v>
+        <v>15960</v>
       </c>
       <c r="M9" t="n">
-        <v>8090</v>
+        <v>11600</v>
       </c>
       <c r="N9" t="n">
-        <v>26.55</v>
+        <v>0.24</v>
       </c>
       <c r="O9" t="n">
-        <v>20624009875</v>
+        <v>223891791260</v>
       </c>
       <c r="P9" t="n">
-        <v>17950</v>
+        <v>28700</v>
       </c>
       <c r="Q9" t="n">
-        <v>8090</v>
+        <v>11600</v>
       </c>
       <c r="R9" t="n">
-        <v>-17000</v>
+        <v>-22000</v>
       </c>
       <c r="S9" t="n">
-        <v>149000</v>
+        <v>0</v>
       </c>
       <c r="T9" t="inlineStr">
         <is>
-          <t>과도한 투자 대비 낮은 시가총액에 대한 비판과 경영 방식에 대한 의문. 공매도와 유증에 대한 부정적 인식.</t>
+          <t>덕산넵코어스 관련 국민권익위 조사 요청 및 사기 상장 의혹 제기.</t>
         </is>
       </c>
       <c r="U9" t="inlineStr"/>
       <c r="V9" t="n">
-        <v>0</v>
+        <v>0.3</v>
       </c>
       <c r="W9" t="inlineStr">
         <is>
-          <t>['시가총액', '공매도', '유증']</t>
+          <t>['덕산넵코어스', '사기상장', '국민권익위']</t>
         </is>
       </c>
       <c r="X9" t="n">
@@ -1287,43 +1287,43 @@
       </c>
       <c r="Y9" t="inlineStr">
         <is>
-          <t>추적</t>
+          <t>활성</t>
         </is>
       </c>
       <c r="Z9" t="inlineStr">
         <is>
-          <t>034220</t>
+          <t>266690</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>본느</t>
+          <t>HLB</t>
         </is>
       </c>
       <c r="B10" t="n">
-        <v>6430</v>
+        <v>45650</v>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>'-0.46%</t>
+          <t>'-0.54%</t>
         </is>
       </c>
       <c r="D10" t="n">
-        <v>-0.31</v>
+        <v>-0.73</v>
       </c>
       <c r="E10" t="n">
-        <v>115</v>
+        <v>377</v>
       </c>
       <c r="F10" t="n">
-        <v>57</v>
+        <v>193</v>
       </c>
       <c r="G10" t="n">
-        <v>240</v>
+        <v>1405</v>
       </c>
       <c r="H10" t="n">
-        <v>0</v>
+        <v>13.39</v>
       </c>
       <c r="I10" t="inlineStr">
         <is>
@@ -1331,91 +1331,91 @@
         </is>
       </c>
       <c r="J10" t="n">
-        <v>6460</v>
+        <v>45900</v>
       </c>
       <c r="K10" t="n">
-        <v>6930</v>
+        <v>45950</v>
       </c>
       <c r="L10" t="n">
-        <v>8390</v>
+        <v>46500</v>
       </c>
       <c r="M10" t="n">
-        <v>6320</v>
+        <v>45100</v>
       </c>
       <c r="N10" t="n">
-        <v>0.31</v>
+        <v>14.12</v>
       </c>
       <c r="O10" t="n">
-        <v>22223988240</v>
+        <v>41028686975</v>
       </c>
       <c r="P10" t="n">
-        <v>9680</v>
+        <v>69200</v>
       </c>
       <c r="Q10" t="n">
-        <v>371</v>
+        <v>24150</v>
       </c>
       <c r="R10" t="n">
-        <v>-28000</v>
+        <v>-53000</v>
       </c>
       <c r="S10" t="n">
-        <v>0</v>
+        <v>-3000</v>
       </c>
       <c r="T10" t="inlineStr">
         <is>
-          <t>관리종목 해제 및 거래 정상화, 새 주인 확정 가능성 언급. 회사 미래 가치 및 불확실성 해소에 따른 긍정적 전망. 주포의 움직임 및 매물대 돌파 기대감.</t>
+          <t>HLB의 간암 치료제 관련 기대감 및 FDA 승인 전망. '리보세라닙 병용요법', '무상증자' 등 구체적인 호재 언급과 함께 높은 목표 주가 제시. 공매도 세력에 대한 비판 및 투자자들의 동요 자제 호소.</t>
         </is>
       </c>
       <c r="U10" t="inlineStr"/>
       <c r="V10" t="n">
-        <v>0</v>
+        <v>0.4</v>
       </c>
       <c r="W10" t="inlineStr">
         <is>
-          <t>['관리종목 해제', '새 주인', '불확실성 해소']</t>
+          <t>['리보세라닙', 'FDA', '무상증자']</t>
         </is>
       </c>
       <c r="X10" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="Y10" t="inlineStr">
         <is>
-          <t>추적</t>
+          <t>활성</t>
         </is>
       </c>
       <c r="Z10" t="inlineStr">
         <is>
-          <t>226340</t>
+          <t>028300</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>삼천당제약</t>
+          <t>본느</t>
         </is>
       </c>
       <c r="B11" t="n">
-        <v>239500</v>
+        <v>6390</v>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>'-0.62%</t>
+          <t>'-1.08%</t>
         </is>
       </c>
       <c r="D11" t="n">
-        <v>-0.65</v>
+        <v>-0.31</v>
       </c>
       <c r="E11" t="n">
-        <v>142</v>
+        <v>117</v>
       </c>
       <c r="F11" t="n">
-        <v>76</v>
+        <v>58</v>
       </c>
       <c r="G11" t="n">
-        <v>948</v>
+        <v>249</v>
       </c>
       <c r="H11" t="n">
-        <v>3.47</v>
+        <v>0</v>
       </c>
       <c r="I11" t="inlineStr">
         <is>
@@ -1423,91 +1423,91 @@
         </is>
       </c>
       <c r="J11" t="n">
-        <v>241000</v>
+        <v>6460</v>
       </c>
       <c r="K11" t="n">
-        <v>227000</v>
+        <v>6930</v>
       </c>
       <c r="L11" t="n">
-        <v>242500</v>
+        <v>8390</v>
       </c>
       <c r="M11" t="n">
-        <v>210500</v>
+        <v>6320</v>
       </c>
       <c r="N11" t="n">
-        <v>4.12</v>
+        <v>0.31</v>
       </c>
       <c r="O11" t="n">
-        <v>55806422750</v>
+        <v>22286162940</v>
       </c>
       <c r="P11" t="n">
-        <v>1233000</v>
+        <v>9680</v>
       </c>
       <c r="Q11" t="n">
-        <v>120000</v>
+        <v>371</v>
       </c>
       <c r="R11" t="n">
-        <v>6000</v>
+        <v>-28000</v>
       </c>
       <c r="S11" t="n">
-        <v>5000</v>
+        <v>0</v>
       </c>
       <c r="T11" t="inlineStr">
         <is>
-          <t>연기금 7일째 매수 및 캐나다 세마 출시 임박, 릴레이 계약 공시 등 긍정적인 뉴스.</t>
+          <t>관리종목 해제 및 거래 정상화, 새 주인 확정 가능성 언급. 회사 미래 가치 및 불확실성 해소에 따른 긍정적 전망. 주포의 움직임 및 매물대 돌파 기대감.</t>
         </is>
       </c>
       <c r="U11" t="inlineStr"/>
       <c r="V11" t="n">
-        <v>0.4</v>
+        <v>0</v>
       </c>
       <c r="W11" t="inlineStr">
         <is>
-          <t>['아일리아', '릴레이계약', '공매도금지']</t>
+          <t>['관리종목 해제', '새 주인', '불확실성 해소']</t>
         </is>
       </c>
       <c r="X11" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="Y11" t="inlineStr">
         <is>
-          <t>활성</t>
+          <t>추적</t>
         </is>
       </c>
       <c r="Z11" t="inlineStr">
         <is>
-          <t>000250</t>
+          <t>226340</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>삼성전자</t>
+          <t>LG디스플레이</t>
         </is>
       </c>
       <c r="B12" t="n">
-        <v>264500</v>
+        <v>8160</v>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>'-1.49%</t>
+          <t>'-1.09%</t>
         </is>
       </c>
       <c r="D12" t="n">
-        <v>0.01</v>
+        <v>-0.17</v>
       </c>
       <c r="E12" t="n">
-        <v>800</v>
+        <v>93</v>
       </c>
       <c r="F12" t="n">
-        <v>552</v>
+        <v>47</v>
       </c>
       <c r="G12" t="n">
-        <v>2447</v>
+        <v>300</v>
       </c>
       <c r="H12" t="n">
-        <v>46.38</v>
+        <v>26.38</v>
       </c>
       <c r="I12" t="inlineStr">
         <is>
@@ -1515,91 +1515,91 @@
         </is>
       </c>
       <c r="J12" t="n">
-        <v>268500</v>
+        <v>8250</v>
       </c>
       <c r="K12" t="n">
-        <v>269500</v>
+        <v>8190</v>
       </c>
       <c r="L12" t="n">
-        <v>270000</v>
+        <v>8320</v>
       </c>
       <c r="M12" t="n">
-        <v>263000</v>
+        <v>8090</v>
       </c>
       <c r="N12" t="n">
-        <v>46.37</v>
+        <v>26.55</v>
       </c>
       <c r="O12" t="n">
-        <v>4141523327500</v>
+        <v>24562858195</v>
       </c>
       <c r="P12" t="n">
-        <v>374500</v>
+        <v>17950</v>
       </c>
       <c r="Q12" t="n">
-        <v>90200</v>
+        <v>8090</v>
       </c>
       <c r="R12" t="n">
-        <v>56000</v>
+        <v>-17000</v>
       </c>
       <c r="S12" t="n">
-        <v>-965000</v>
+        <v>149000</v>
       </c>
       <c r="T12" t="inlineStr">
         <is>
-          <t>삼성전자 역대급 영업이익에도 불구하고 주주환원 부족 및 주가 부양 부재에 대한 불만 고조. 국내 증시 전반에 대한 부정적 인식.</t>
+          <t>과도한 투자 대비 낮은 시가총액에 대한 비판과 경영 방식에 대한 의문. 공매도와 유증에 대한 부정적 인식.</t>
         </is>
       </c>
       <c r="U12" t="inlineStr"/>
       <c r="V12" t="n">
-        <v>0.1</v>
+        <v>0</v>
       </c>
       <c r="W12" t="inlineStr">
         <is>
-          <t>['영업이익', '주주환원', '국내 증시']</t>
+          <t>['시가총액', '공매도', '유증']</t>
         </is>
       </c>
       <c r="X12" t="n">
-        <v>8</v>
+        <v>1</v>
       </c>
       <c r="Y12" t="inlineStr">
         <is>
-          <t>활성</t>
+          <t>추적</t>
         </is>
       </c>
       <c r="Z12" t="inlineStr">
         <is>
-          <t>005930</t>
+          <t>034220</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>SK하이닉스</t>
+          <t>삼성전자</t>
         </is>
       </c>
       <c r="B13" t="n">
-        <v>1697000</v>
+        <v>262000</v>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>'-1.51%</t>
+          <t>'-2.42%</t>
         </is>
       </c>
       <c r="D13" t="n">
-        <v>-0.12</v>
+        <v>0.01</v>
       </c>
       <c r="E13" t="n">
         <v>800</v>
       </c>
       <c r="F13" t="n">
-        <v>447</v>
+        <v>543</v>
       </c>
       <c r="G13" t="n">
-        <v>1670</v>
+        <v>2520</v>
       </c>
       <c r="H13" t="n">
-        <v>49.59</v>
+        <v>46.38</v>
       </c>
       <c r="I13" t="inlineStr">
         <is>
@@ -1607,47 +1607,47 @@
         </is>
       </c>
       <c r="J13" t="n">
-        <v>1723000</v>
+        <v>268500</v>
       </c>
       <c r="K13" t="n">
-        <v>1722000</v>
+        <v>269500</v>
       </c>
       <c r="L13" t="n">
-        <v>1759000</v>
+        <v>270000</v>
       </c>
       <c r="M13" t="n">
-        <v>1692000</v>
+        <v>262000</v>
       </c>
       <c r="N13" t="n">
-        <v>49.71</v>
+        <v>46.37</v>
       </c>
       <c r="O13" t="n">
-        <v>3923707669000</v>
+        <v>5187816135500</v>
       </c>
       <c r="P13" t="n">
-        <v>2987000</v>
+        <v>374500</v>
       </c>
       <c r="Q13" t="n">
-        <v>403000</v>
+        <v>90200</v>
       </c>
       <c r="R13" t="n">
-        <v>17000</v>
+        <v>56000</v>
       </c>
       <c r="S13" t="n">
-        <v>-84000</v>
+        <v>-965000</v>
       </c>
       <c r="T13" t="inlineStr">
         <is>
-          <t>SK하이닉스 관련 부정적인 게시글 다수. 주가 조작 의혹 및 정부 정책에 대한 비판. 한국 증시 전반에 대한 불신.</t>
+          <t>삼성전자의 높은 영업이익에도 불구하고 주주환원 정책 미흡 및 국내 증시 전반의 불신 표출. 정치적 이슈와 맞물린 증시 왜곡 및 외인 자금 유출입에 대한 비판.</t>
         </is>
       </c>
       <c r="U13" t="inlineStr"/>
       <c r="V13" t="n">
-        <v>0.1</v>
+        <v>0.2</v>
       </c>
       <c r="W13" t="inlineStr">
         <is>
-          <t>['주가 조작', '정부 정책', '한국 증시']</t>
+          <t>['영업이익', '주주환원', '공매도']</t>
         </is>
       </c>
       <c r="X13" t="n">
@@ -1660,38 +1660,38 @@
       </c>
       <c r="Z13" t="inlineStr">
         <is>
-          <t>000660</t>
+          <t>005930</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>삼성중공업</t>
+          <t>SK하이닉스</t>
         </is>
       </c>
       <c r="B14" t="n">
-        <v>18950</v>
+        <v>1681000</v>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>'-3.02%</t>
+          <t>'-2.44%</t>
         </is>
       </c>
       <c r="D14" t="n">
-        <v>0.01</v>
+        <v>-0.12</v>
       </c>
       <c r="E14" t="n">
-        <v>151</v>
+        <v>800</v>
       </c>
       <c r="F14" t="n">
-        <v>82</v>
+        <v>438</v>
       </c>
       <c r="G14" t="n">
-        <v>434</v>
+        <v>1765</v>
       </c>
       <c r="H14" t="n">
-        <v>27.68</v>
+        <v>49.59</v>
       </c>
       <c r="I14" t="inlineStr">
         <is>
@@ -1699,38 +1699,38 @@
         </is>
       </c>
       <c r="J14" t="n">
-        <v>19540</v>
+        <v>1723000</v>
       </c>
       <c r="K14" t="n">
-        <v>19490</v>
+        <v>1722000</v>
       </c>
       <c r="L14" t="n">
-        <v>19500</v>
+        <v>1759000</v>
       </c>
       <c r="M14" t="n">
-        <v>18850</v>
+        <v>1681000</v>
       </c>
       <c r="N14" t="n">
-        <v>27.67</v>
+        <v>49.71</v>
       </c>
       <c r="O14" t="n">
-        <v>52205842790</v>
+        <v>5182079054000</v>
       </c>
       <c r="P14" t="n">
-        <v>35350</v>
+        <v>2987000</v>
       </c>
       <c r="Q14" t="n">
-        <v>18440</v>
+        <v>403000</v>
       </c>
       <c r="R14" t="n">
-        <v>-449000</v>
+        <v>17000</v>
       </c>
       <c r="S14" t="n">
-        <v>-78000</v>
+        <v>-84000</v>
       </c>
       <c r="T14" t="inlineStr">
         <is>
-          <t>삼성중공업 실적 전망에 대한 부정적인 의견과 목표가 하향 소식. 조선주 전반의 하락세 및 주가 부양 부재에 대한 불만.</t>
+          <t>SK하이닉스의 급격한 주가 하락 및 국내 증시 전반에 대한 불만 표출. 정치적 요인과 맞물린 증시 불안정 및 기관·외인의 의도적인 주가 조작 의혹 제기.</t>
         </is>
       </c>
       <c r="U14" t="inlineStr"/>
@@ -1739,11 +1739,11 @@
       </c>
       <c r="W14" t="inlineStr">
         <is>
-          <t>['실적', '조선주', '목표가']</t>
+          <t>['주가', '증시', '공매도']</t>
         </is>
       </c>
       <c r="X14" t="n">
-        <v>5</v>
+        <v>8</v>
       </c>
       <c r="Y14" t="inlineStr">
         <is>
@@ -1752,77 +1752,77 @@
       </c>
       <c r="Z14" t="inlineStr">
         <is>
-          <t>010140</t>
+          <t>000660</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>대한광통신</t>
+          <t>두산에너빌리티</t>
         </is>
       </c>
       <c r="B15" t="n">
-        <v>16970</v>
+        <v>78000</v>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>'-5.41%</t>
+          <t>'-3.11%</t>
         </is>
       </c>
       <c r="D15" t="n">
-        <v>-0.95</v>
+        <v>-0.1</v>
       </c>
       <c r="E15" t="n">
-        <v>148</v>
+        <v>493</v>
       </c>
       <c r="F15" t="n">
-        <v>86</v>
+        <v>289</v>
       </c>
       <c r="G15" t="n">
-        <v>601</v>
+        <v>1553</v>
       </c>
       <c r="H15" t="n">
-        <v>3.97</v>
+        <v>22.49</v>
       </c>
       <c r="I15" t="inlineStr">
         <is>
-          <t>MarketType.KOSDAQ</t>
+          <t>MarketType.KOSPI</t>
         </is>
       </c>
       <c r="J15" t="n">
-        <v>17940</v>
+        <v>80500</v>
       </c>
       <c r="K15" t="n">
-        <v>17770</v>
+        <v>79600</v>
       </c>
       <c r="L15" t="n">
-        <v>17940</v>
+        <v>79600</v>
       </c>
       <c r="M15" t="n">
-        <v>16750</v>
+        <v>75200</v>
       </c>
       <c r="N15" t="n">
-        <v>4.92</v>
+        <v>22.59</v>
       </c>
       <c r="O15" t="n">
-        <v>103559887120</v>
+        <v>328718171450</v>
       </c>
       <c r="P15" t="n">
-        <v>31500</v>
+        <v>139200</v>
       </c>
       <c r="Q15" t="n">
-        <v>1272</v>
+        <v>57000</v>
       </c>
       <c r="R15" t="n">
-        <v>-412000</v>
+        <v>-650000</v>
       </c>
       <c r="S15" t="n">
-        <v>-70000</v>
+        <v>-117000</v>
       </c>
       <c r="T15" t="inlineStr">
         <is>
-          <t>미국 광통신주 하락 영향 및 외인/기관 쌍매도, 프로그램 매매 불안정성 지적.</t>
+          <t>두산에너빌리티 관련 긍정적인 해외 발전소 건설 및 관세 인하 가능성 언급. 그러나 공매도 및 정부 정책에 대한 불만도 제기.</t>
         </is>
       </c>
       <c r="U15" t="inlineStr"/>
@@ -1831,11 +1831,11 @@
       </c>
       <c r="W15" t="inlineStr">
         <is>
-          <t>['광통신', '외인/기관', '프로그램 매매']</t>
+          <t>['가스발전', '원전', '공매도']</t>
         </is>
       </c>
       <c r="X15" t="n">
-        <v>8</v>
+        <v>2</v>
       </c>
       <c r="Y15" t="inlineStr">
         <is>
@@ -1844,38 +1844,38 @@
       </c>
       <c r="Z15" t="inlineStr">
         <is>
-          <t>010170</t>
+          <t>034020</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>대한전선</t>
+          <t>삼성중공업</t>
         </is>
       </c>
       <c r="B16" t="n">
-        <v>28075</v>
+        <v>18860</v>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>'-5.79%</t>
+          <t>'-3.48%</t>
         </is>
       </c>
       <c r="D16" t="n">
-        <v>-0.76</v>
+        <v>0.01</v>
       </c>
       <c r="E16" t="n">
-        <v>82</v>
+        <v>155</v>
       </c>
       <c r="F16" t="n">
-        <v>57</v>
+        <v>84</v>
       </c>
       <c r="G16" t="n">
-        <v>223</v>
+        <v>453</v>
       </c>
       <c r="H16" t="n">
-        <v>10.02</v>
+        <v>27.68</v>
       </c>
       <c r="I16" t="inlineStr">
         <is>
@@ -1883,60 +1883,60 @@
         </is>
       </c>
       <c r="J16" t="n">
-        <v>29800</v>
+        <v>19540</v>
       </c>
       <c r="K16" t="n">
-        <v>29900</v>
+        <v>19490</v>
       </c>
       <c r="L16" t="n">
-        <v>30000</v>
+        <v>19500</v>
       </c>
       <c r="M16" t="n">
-        <v>28050</v>
+        <v>18850</v>
       </c>
       <c r="N16" t="n">
-        <v>10.78</v>
+        <v>27.67</v>
       </c>
       <c r="O16" t="n">
-        <v>73534592700</v>
+        <v>67113974970</v>
       </c>
       <c r="P16" t="n">
-        <v>75900</v>
+        <v>35350</v>
       </c>
       <c r="Q16" t="n">
-        <v>15960</v>
+        <v>18440</v>
       </c>
       <c r="R16" t="n">
-        <v>-612000</v>
+        <v>-449000</v>
       </c>
       <c r="S16" t="n">
-        <v>1000</v>
+        <v>-78000</v>
       </c>
       <c r="T16" t="inlineStr">
         <is>
-          <t>연이은 주가 하락(-11%) 및 공매도 프로그램 이용 외국인에 대한 비판. 유상증자 및 고점 물량 부담에 대한 우려 제기.</t>
+          <t>삼성중공업 실적 전망에 대한 부정적인 의견과 목표가 하향 소식. 조선주 전반의 하락세 및 주가 부양 부재에 대한 불만.</t>
         </is>
       </c>
       <c r="U16" t="inlineStr"/>
       <c r="V16" t="n">
-        <v>0</v>
+        <v>0.1</v>
       </c>
       <c r="W16" t="inlineStr">
         <is>
-          <t>['주가 하락', '공매도', '유상증자']</t>
+          <t>['실적', '조선주', '목표가']</t>
         </is>
       </c>
       <c r="X16" t="n">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="Y16" t="inlineStr">
         <is>
-          <t>추적</t>
+          <t>활성</t>
         </is>
       </c>
       <c r="Z16" t="inlineStr">
         <is>
-          <t>001440</t>
+          <t>010140</t>
         </is>
       </c>
     </row>
@@ -1947,24 +1947,24 @@
         </is>
       </c>
       <c r="B17" t="n">
-        <v>4170</v>
+        <v>4270</v>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>'-5.87%</t>
+          <t>'-3.61%</t>
         </is>
       </c>
       <c r="D17" t="n">
         <v>1.19</v>
       </c>
       <c r="E17" t="n">
-        <v>142</v>
+        <v>145</v>
       </c>
       <c r="F17" t="n">
-        <v>90</v>
+        <v>92</v>
       </c>
       <c r="G17" t="n">
-        <v>210</v>
+        <v>220</v>
       </c>
       <c r="H17" t="n">
         <v>4.46</v>
@@ -1990,7 +1990,7 @@
         <v>3.27</v>
       </c>
       <c r="O17" t="n">
-        <v>93390784816</v>
+        <v>93837806846</v>
       </c>
       <c r="P17" t="n">
         <v>5470</v>
@@ -2006,16 +2006,16 @@
       </c>
       <c r="T17" t="inlineStr">
         <is>
-          <t>러시아 전염병 관련 소식으로 국제약품에 대한 기대감 형성. WHO의 상황 파악 지연 및 사망자 발생 소식이 혼재.</t>
+          <t>미국 항생제 보유 회사 주가 급등 및 WHO의 러시아 폐렴 관련 불확실성 속 국제 약품 관련 기대감 표출. 다만, 사망자 수 관련 상반된 보도 및 국제 정세 불안으로 인한 투자 심리 위축 우려.</t>
         </is>
       </c>
       <c r="U17" t="inlineStr"/>
       <c r="V17" t="n">
-        <v>0.2</v>
+        <v>0.1</v>
       </c>
       <c r="W17" t="inlineStr">
         <is>
-          <t>['전염병', '러시아', 'WHO']</t>
+          <t>['항생제', '전염병', '국제']</t>
         </is>
       </c>
       <c r="X17" t="n">
@@ -2035,31 +2035,31 @@
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>두산에너빌리티</t>
+          <t>대우건설</t>
         </is>
       </c>
       <c r="B18" t="n">
-        <v>75500</v>
+        <v>16670</v>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>'-6.21%</t>
+          <t>'-3.86%</t>
         </is>
       </c>
       <c r="D18" t="n">
-        <v>-0.1</v>
+        <v>-0.04</v>
       </c>
       <c r="E18" t="n">
-        <v>484</v>
+        <v>137</v>
       </c>
       <c r="F18" t="n">
-        <v>284</v>
+        <v>60</v>
       </c>
       <c r="G18" t="n">
-        <v>1542</v>
+        <v>719</v>
       </c>
       <c r="H18" t="n">
-        <v>22.49</v>
+        <v>9.460000000000001</v>
       </c>
       <c r="I18" t="inlineStr">
         <is>
@@ -2067,38 +2067,38 @@
         </is>
       </c>
       <c r="J18" t="n">
-        <v>80500</v>
+        <v>17340</v>
       </c>
       <c r="K18" t="n">
-        <v>79600</v>
+        <v>17190</v>
       </c>
       <c r="L18" t="n">
-        <v>79600</v>
+        <v>17220</v>
       </c>
       <c r="M18" t="n">
-        <v>75200</v>
+        <v>16660</v>
       </c>
       <c r="N18" t="n">
-        <v>22.59</v>
+        <v>9.5</v>
       </c>
       <c r="O18" t="n">
-        <v>256653035450</v>
+        <v>57542446855</v>
       </c>
       <c r="P18" t="n">
-        <v>139200</v>
+        <v>40350</v>
       </c>
       <c r="Q18" t="n">
-        <v>57000</v>
+        <v>3320</v>
       </c>
       <c r="R18" t="n">
-        <v>-650000</v>
+        <v>-58000</v>
       </c>
       <c r="S18" t="n">
-        <v>-117000</v>
+        <v>-36000</v>
       </c>
       <c r="T18" t="inlineStr">
         <is>
-          <t>두산에너빌리티 관련 긍정적인 해외 발전소 건설 및 관세 인하 가능성 언급. 그러나 공매도 및 정부 정책에 대한 불만도 제기.</t>
+          <t>대우건설 주가 조작 및 공매도에 대한 의혹 제기. 주주 호소 및 대차 해지의 중요성 강조. 금융 시장 전반에 대한 불신.</t>
         </is>
       </c>
       <c r="U18" t="inlineStr"/>
@@ -2107,11 +2107,11 @@
       </c>
       <c r="W18" t="inlineStr">
         <is>
-          <t>['가스발전', '원전', '공매도']</t>
+          <t>['주가 조작', '공매도', '대차 해지']</t>
         </is>
       </c>
       <c r="X18" t="n">
-        <v>2</v>
+        <v>8</v>
       </c>
       <c r="Y18" t="inlineStr">
         <is>
@@ -2120,77 +2120,77 @@
       </c>
       <c r="Z18" t="inlineStr">
         <is>
-          <t>034020</t>
+          <t>047040</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>대우건설</t>
+          <t>대한광통신</t>
         </is>
       </c>
       <c r="B19" t="n">
-        <v>16670</v>
+        <v>16970</v>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>'-6.30%</t>
+          <t>'-5.41%</t>
         </is>
       </c>
       <c r="D19" t="n">
-        <v>-0.04</v>
+        <v>-0.95</v>
       </c>
       <c r="E19" t="n">
-        <v>132</v>
+        <v>153</v>
       </c>
       <c r="F19" t="n">
-        <v>60</v>
+        <v>90</v>
       </c>
       <c r="G19" t="n">
-        <v>705</v>
+        <v>610</v>
       </c>
       <c r="H19" t="n">
-        <v>9.460000000000001</v>
+        <v>3.97</v>
       </c>
       <c r="I19" t="inlineStr">
         <is>
-          <t>MarketType.KOSPI</t>
+          <t>MarketType.KOSDAQ</t>
         </is>
       </c>
       <c r="J19" t="n">
-        <v>17790</v>
+        <v>17940</v>
       </c>
       <c r="K19" t="n">
-        <v>0</v>
+        <v>17770</v>
       </c>
       <c r="L19" t="n">
-        <v>0</v>
+        <v>17940</v>
       </c>
       <c r="M19" t="n">
-        <v>0</v>
+        <v>16750</v>
       </c>
       <c r="N19" t="n">
-        <v>9.5</v>
+        <v>4.92</v>
       </c>
       <c r="O19" t="n">
-        <v>50634000000</v>
+        <v>104127279070</v>
       </c>
       <c r="P19" t="n">
-        <v>0</v>
+        <v>31500</v>
       </c>
       <c r="Q19" t="n">
-        <v>0</v>
+        <v>1272</v>
       </c>
       <c r="R19" t="n">
-        <v>-58000</v>
+        <v>-412000</v>
       </c>
       <c r="S19" t="n">
-        <v>-36000</v>
+        <v>-70000</v>
       </c>
       <c r="T19" t="inlineStr">
         <is>
-          <t>대우건설 주가 조작 및 공매도에 대한 의혹 제기. 주주 호소 및 대차 해지의 중요성 강조. 금융 시장 전반에 대한 불신.</t>
+          <t>미국 광통신주 하락 영향 및 외인/기관 쌍매도, 프로그램 매매 불안정성 지적.</t>
         </is>
       </c>
       <c r="U19" t="inlineStr"/>
@@ -2199,7 +2199,7 @@
       </c>
       <c r="W19" t="inlineStr">
         <is>
-          <t>['주가 조작', '공매도', '대차 해지']</t>
+          <t>['광통신', '외인/기관', '프로그램 매매']</t>
         </is>
       </c>
       <c r="X19" t="n">
@@ -2212,169 +2212,169 @@
       </c>
       <c r="Z19" t="inlineStr">
         <is>
-          <t>047040</t>
+          <t>010170</t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>빛과전자</t>
+          <t>한미사이언스</t>
         </is>
       </c>
       <c r="B20" t="n">
-        <v>4870</v>
+        <v>54900</v>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>'-6.53%</t>
+          <t>'-5.51%</t>
         </is>
       </c>
       <c r="D20" t="n">
-        <v>-0.07000000000000001</v>
+        <v>0.02</v>
       </c>
       <c r="E20" t="n">
-        <v>98</v>
+        <v>363</v>
       </c>
       <c r="F20" t="n">
-        <v>62</v>
+        <v>166</v>
       </c>
       <c r="G20" t="n">
-        <v>364</v>
+        <v>810</v>
       </c>
       <c r="H20" t="n">
-        <v>4.65</v>
+        <v>1.32</v>
       </c>
       <c r="I20" t="inlineStr">
         <is>
-          <t>MarketType.KOSDAQ</t>
+          <t>MarketType.KOSPI</t>
         </is>
       </c>
       <c r="J20" t="n">
-        <v>5210</v>
+        <v>58100</v>
       </c>
       <c r="K20" t="n">
-        <v>5220</v>
+        <v>63200</v>
       </c>
       <c r="L20" t="n">
-        <v>5310</v>
+        <v>63800</v>
       </c>
       <c r="M20" t="n">
-        <v>4755</v>
+        <v>51700</v>
       </c>
       <c r="N20" t="n">
-        <v>4.72</v>
+        <v>1.3</v>
       </c>
       <c r="O20" t="n">
-        <v>73448248340</v>
+        <v>64488721150</v>
       </c>
       <c r="P20" t="n">
-        <v>8100</v>
+        <v>63800</v>
       </c>
       <c r="Q20" t="n">
-        <v>592</v>
+        <v>25600</v>
       </c>
       <c r="R20" t="n">
-        <v>-106000</v>
+        <v>-167000</v>
       </c>
       <c r="S20" t="n">
-        <v>0</v>
+        <v>-48000</v>
       </c>
       <c r="T20" t="inlineStr">
         <is>
-          <t>전환사채 발행 및 장내 매도에 대한 우려. 광트랜시버 사업 전망에 대한 기대와 함께 급등 가능성에 대한 언급.</t>
+          <t>한미사이언스 주가 조작 및 악질적인 주가 부양 행태에 대한 강한 비판. 신약 승인 재료에도 불구하고 하한가 기록.</t>
         </is>
       </c>
       <c r="U20" t="inlineStr"/>
       <c r="V20" t="n">
-        <v>0</v>
+        <v>0.1</v>
       </c>
       <c r="W20" t="inlineStr">
         <is>
-          <t>['전환사채', '광트랜시버', '장내매도']</t>
+          <t>['주가 조작', '신약', '하한가']</t>
         </is>
       </c>
       <c r="X20" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="Y20" t="inlineStr">
         <is>
-          <t>추적</t>
+          <t>활성</t>
         </is>
       </c>
       <c r="Z20" t="inlineStr">
         <is>
-          <t>069540</t>
+          <t>008930</t>
         </is>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>라온시큐어</t>
+          <t>대한전선</t>
         </is>
       </c>
       <c r="B21" t="n">
-        <v>15350</v>
+        <v>28100</v>
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>'-8.14%</t>
+          <t>'-5.70%</t>
         </is>
       </c>
       <c r="D21" t="n">
-        <v>-1.44</v>
+        <v>-0.76</v>
       </c>
       <c r="E21" t="n">
-        <v>64</v>
+        <v>82</v>
       </c>
       <c r="F21" t="n">
-        <v>41</v>
+        <v>57</v>
       </c>
       <c r="G21" t="n">
-        <v>208</v>
+        <v>227</v>
       </c>
       <c r="H21" t="n">
-        <v>0.93</v>
+        <v>10.02</v>
       </c>
       <c r="I21" t="inlineStr">
         <is>
-          <t>MarketType.KOSDAQ</t>
+          <t>MarketType.KOSPI</t>
         </is>
       </c>
       <c r="J21" t="n">
-        <v>16710</v>
+        <v>29800</v>
       </c>
       <c r="K21" t="n">
-        <v>16460</v>
+        <v>29900</v>
       </c>
       <c r="L21" t="n">
-        <v>17180</v>
+        <v>30000</v>
       </c>
       <c r="M21" t="n">
-        <v>14820</v>
+        <v>28050</v>
       </c>
       <c r="N21" t="n">
-        <v>2.37</v>
+        <v>10.78</v>
       </c>
       <c r="O21" t="n">
-        <v>37513928820</v>
+        <v>77461483400</v>
       </c>
       <c r="P21" t="n">
-        <v>17590</v>
+        <v>75900</v>
       </c>
       <c r="Q21" t="n">
-        <v>6320</v>
+        <v>15960</v>
       </c>
       <c r="R21" t="n">
-        <v>10000</v>
+        <v>-612000</v>
       </c>
       <c r="S21" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="T21" t="inlineStr">
         <is>
-          <t>KDB생명 해킹 방어 성공 및 AI 사이버보안 협의체 선정 뉴스. SKT와의 협력 기반 역대 고점 돌파 기대.</t>
+          <t>연이은 주가 하락(-11%) 및 공매도 프로그램 이용 외국인에 대한 비판. 유상증자 및 고점 물량 부담에 대한 우려 제기.</t>
         </is>
       </c>
       <c r="U21" t="inlineStr"/>
@@ -2383,7 +2383,7 @@
       </c>
       <c r="W21" t="inlineStr">
         <is>
-          <t>['양자보안', 'AI', '사이버보안']</t>
+          <t>['주가 하락', '공매도', '유상증자']</t>
         </is>
       </c>
       <c r="X21" t="n">
@@ -2396,130 +2396,130 @@
       </c>
       <c r="Z21" t="inlineStr">
         <is>
-          <t>042510</t>
+          <t>001440</t>
         </is>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>한미사이언스</t>
+          <t>빛과전자</t>
         </is>
       </c>
       <c r="B22" t="n">
-        <v>52800</v>
+        <v>4870</v>
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>'-9.12%</t>
+          <t>'-6.53%</t>
         </is>
       </c>
       <c r="D22" t="n">
-        <v>0.02</v>
+        <v>-0.07000000000000001</v>
       </c>
       <c r="E22" t="n">
-        <v>356</v>
+        <v>100</v>
       </c>
       <c r="F22" t="n">
-        <v>164</v>
+        <v>63</v>
       </c>
       <c r="G22" t="n">
-        <v>799</v>
+        <v>367</v>
       </c>
       <c r="H22" t="n">
-        <v>1.32</v>
+        <v>4.65</v>
       </c>
       <c r="I22" t="inlineStr">
         <is>
-          <t>MarketType.KOSPI</t>
+          <t>MarketType.KOSDAQ</t>
         </is>
       </c>
       <c r="J22" t="n">
-        <v>58100</v>
+        <v>5210</v>
       </c>
       <c r="K22" t="n">
-        <v>63200</v>
+        <v>5220</v>
       </c>
       <c r="L22" t="n">
-        <v>63800</v>
+        <v>5310</v>
       </c>
       <c r="M22" t="n">
-        <v>51700</v>
+        <v>4755</v>
       </c>
       <c r="N22" t="n">
-        <v>1.3</v>
+        <v>4.72</v>
       </c>
       <c r="O22" t="n">
-        <v>59764795750</v>
+        <v>73705496350</v>
       </c>
       <c r="P22" t="n">
-        <v>63800</v>
+        <v>8100</v>
       </c>
       <c r="Q22" t="n">
-        <v>25600</v>
+        <v>592</v>
       </c>
       <c r="R22" t="n">
-        <v>-167000</v>
+        <v>-106000</v>
       </c>
       <c r="S22" t="n">
-        <v>-48000</v>
+        <v>0</v>
       </c>
       <c r="T22" t="inlineStr">
         <is>
-          <t>한미사이언스 주가 조작 및 악질적인 주가 부양 행태에 대한 강한 비판. 신약 승인 재료에도 불구하고 하한가 기록.</t>
+          <t>전환사채 발행 및 장내 매도에 대한 우려. 광트랜시버 사업 전망에 대한 기대와 함께 급등 가능성에 대한 언급.</t>
         </is>
       </c>
       <c r="U22" t="inlineStr"/>
       <c r="V22" t="n">
-        <v>0.1</v>
+        <v>0</v>
       </c>
       <c r="W22" t="inlineStr">
         <is>
-          <t>['주가 조작', '신약', '하한가']</t>
+          <t>['전환사채', '광트랜시버', '장내매도']</t>
         </is>
       </c>
       <c r="X22" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="Y22" t="inlineStr">
         <is>
-          <t>활성</t>
+          <t>추적</t>
         </is>
       </c>
       <c r="Z22" t="inlineStr">
         <is>
-          <t>008930</t>
+          <t>069540</t>
         </is>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>삼표시멘트</t>
+          <t>라온시큐어</t>
         </is>
       </c>
       <c r="B23" t="n">
-        <v>7020</v>
+        <v>15390</v>
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>'-10.23%</t>
+          <t>'-7.90%</t>
         </is>
       </c>
       <c r="D23" t="n">
-        <v>-2.03</v>
+        <v>-1.44</v>
       </c>
       <c r="E23" t="n">
-        <v>242</v>
+        <v>66</v>
       </c>
       <c r="F23" t="n">
-        <v>104</v>
+        <v>41</v>
       </c>
       <c r="G23" t="n">
-        <v>697</v>
+        <v>210</v>
       </c>
       <c r="H23" t="n">
-        <v>3.09</v>
+        <v>0.93</v>
       </c>
       <c r="I23" t="inlineStr">
         <is>
@@ -2527,47 +2527,47 @@
         </is>
       </c>
       <c r="J23" t="n">
-        <v>7820</v>
+        <v>16710</v>
       </c>
       <c r="K23" t="n">
-        <v>8080</v>
+        <v>16460</v>
       </c>
       <c r="L23" t="n">
-        <v>8510</v>
+        <v>17180</v>
       </c>
       <c r="M23" t="n">
-        <v>6870</v>
+        <v>14820</v>
       </c>
       <c r="N23" t="n">
-        <v>5.12</v>
+        <v>2.37</v>
       </c>
       <c r="O23" t="n">
-        <v>98326755395</v>
+        <v>37860696300</v>
       </c>
       <c r="P23" t="n">
-        <v>23500</v>
+        <v>17590</v>
       </c>
       <c r="Q23" t="n">
-        <v>2890</v>
+        <v>6320</v>
       </c>
       <c r="R23" t="n">
-        <v>-516000</v>
+        <v>10000</v>
       </c>
       <c r="S23" t="n">
         <v>0</v>
       </c>
       <c r="T23" t="inlineStr">
         <is>
-          <t>삼표시멘트의 본PF 구성 및 부동산 관련 소식과 함께 공매도 및 주가 움직임에 대한 언급.</t>
+          <t>KDB생명 해킹 방어 성공 및 AI 사이버보안 협의체 선정 뉴스. SKT와의 협력 기반 역대 고점 돌파 기대.</t>
         </is>
       </c>
       <c r="U23" t="inlineStr"/>
       <c r="V23" t="n">
-        <v>0.3</v>
+        <v>0</v>
       </c>
       <c r="W23" t="inlineStr">
         <is>
-          <t>['본PF', '공매도', '부동산']</t>
+          <t>['양자보안', 'AI', '사이버보안']</t>
         </is>
       </c>
       <c r="X23" t="n">
@@ -2575,82 +2575,82 @@
       </c>
       <c r="Y23" t="inlineStr">
         <is>
-          <t>활성</t>
+          <t>추적</t>
         </is>
       </c>
       <c r="Z23" t="inlineStr">
         <is>
-          <t>038500</t>
+          <t>042510</t>
         </is>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>신풍제약</t>
+          <t>삼표시멘트</t>
         </is>
       </c>
       <c r="B24" t="n">
-        <v>9780</v>
+        <v>7080</v>
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>'-11.17%</t>
+          <t>'-9.46%</t>
         </is>
       </c>
       <c r="D24" t="n">
-        <v>0.03</v>
+        <v>-2.03</v>
       </c>
       <c r="E24" t="n">
-        <v>124</v>
+        <v>249</v>
       </c>
       <c r="F24" t="n">
-        <v>65</v>
+        <v>107</v>
       </c>
       <c r="G24" t="n">
-        <v>394</v>
+        <v>709</v>
       </c>
       <c r="H24" t="n">
-        <v>5.04</v>
+        <v>3.09</v>
       </c>
       <c r="I24" t="inlineStr">
         <is>
-          <t>MarketType.KOSPI</t>
+          <t>MarketType.KOSDAQ</t>
         </is>
       </c>
       <c r="J24" t="n">
-        <v>11010</v>
+        <v>7820</v>
       </c>
       <c r="K24" t="n">
-        <v>10110</v>
+        <v>8080</v>
       </c>
       <c r="L24" t="n">
-        <v>10130</v>
+        <v>8510</v>
       </c>
       <c r="M24" t="n">
-        <v>9750</v>
+        <v>6870</v>
       </c>
       <c r="N24" t="n">
-        <v>5.01</v>
+        <v>5.12</v>
       </c>
       <c r="O24" t="n">
-        <v>7756060400</v>
+        <v>98641227755</v>
       </c>
       <c r="P24" t="n">
-        <v>15900</v>
+        <v>23500</v>
       </c>
       <c r="Q24" t="n">
-        <v>6310</v>
+        <v>2890</v>
       </c>
       <c r="R24" t="n">
-        <v>-325000</v>
+        <v>-516000</v>
       </c>
       <c r="S24" t="n">
         <v>0</v>
       </c>
       <c r="T24" t="inlineStr">
         <is>
-          <t>신풍제약 관련 바이러스 테마주로서의 기대감 형성. 자사주 매집 물량 언급 및 상승 가능성 제시. 일부 매도세에 대한 경계.</t>
+          <t>삼표시멘트의 주가 하락세 지속 및 대규모 투자 유치 관련 불확실성. '본PF', '대주단 구성' 등 주요 투자 이벤트 언급에도 불구하고 주가 부진 및 공매도 세력에 대한 비판.</t>
         </is>
       </c>
       <c r="U24" t="inlineStr"/>
@@ -2659,7 +2659,7 @@
       </c>
       <c r="W24" t="inlineStr">
         <is>
-          <t>['바이러스', '자사주', '테마주']</t>
+          <t>['본PF', '대주단', '공매도']</t>
         </is>
       </c>
       <c r="X24" t="n">
@@ -2671,6 +2671,98 @@
         </is>
       </c>
       <c r="Z24" t="inlineStr">
+        <is>
+          <t>038500</t>
+        </is>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" t="inlineStr">
+        <is>
+          <t>신풍제약</t>
+        </is>
+      </c>
+      <c r="B25" t="n">
+        <v>9780</v>
+      </c>
+      <c r="C25" t="inlineStr">
+        <is>
+          <t>'-11.17%</t>
+        </is>
+      </c>
+      <c r="D25" t="n">
+        <v>0.03</v>
+      </c>
+      <c r="E25" t="n">
+        <v>127</v>
+      </c>
+      <c r="F25" t="n">
+        <v>66</v>
+      </c>
+      <c r="G25" t="n">
+        <v>399</v>
+      </c>
+      <c r="H25" t="n">
+        <v>5.04</v>
+      </c>
+      <c r="I25" t="inlineStr">
+        <is>
+          <t>MarketType.KOSPI</t>
+        </is>
+      </c>
+      <c r="J25" t="n">
+        <v>11010</v>
+      </c>
+      <c r="K25" t="n">
+        <v>10110</v>
+      </c>
+      <c r="L25" t="n">
+        <v>10130</v>
+      </c>
+      <c r="M25" t="n">
+        <v>9750</v>
+      </c>
+      <c r="N25" t="n">
+        <v>5.01</v>
+      </c>
+      <c r="O25" t="n">
+        <v>7843307780</v>
+      </c>
+      <c r="P25" t="n">
+        <v>15900</v>
+      </c>
+      <c r="Q25" t="n">
+        <v>6310</v>
+      </c>
+      <c r="R25" t="n">
+        <v>-325000</v>
+      </c>
+      <c r="S25" t="n">
+        <v>0</v>
+      </c>
+      <c r="T25" t="inlineStr">
+        <is>
+          <t>신풍제약 관련 바이러스 테마주로서의 기대감 형성. 자사주 매집 물량 언급 및 상승 가능성 제시. 일부 매도세에 대한 경계.</t>
+        </is>
+      </c>
+      <c r="U25" t="inlineStr"/>
+      <c r="V25" t="n">
+        <v>0.2</v>
+      </c>
+      <c r="W25" t="inlineStr">
+        <is>
+          <t>['바이러스', '자사주', '테마주']</t>
+        </is>
+      </c>
+      <c r="X25" t="n">
+        <v>2</v>
+      </c>
+      <c r="Y25" t="inlineStr">
+        <is>
+          <t>활성</t>
+        </is>
+      </c>
+      <c r="Z25" t="inlineStr">
         <is>
           <t>019170</t>
         </is>

--- a/data/trending_integrated_20261008_15.xlsx
+++ b/data/trending_integrated_20261008_15.xlsx
@@ -584,7 +584,7 @@
         <v>47</v>
       </c>
       <c r="G2" t="n">
-        <v>244</v>
+        <v>245</v>
       </c>
       <c r="H2" t="n">
         <v>0.2</v>
@@ -670,13 +670,13 @@
         <v>-0.08</v>
       </c>
       <c r="E3" t="n">
-        <v>124</v>
+        <v>115</v>
       </c>
       <c r="F3" t="n">
         <v>57</v>
       </c>
       <c r="G3" t="n">
-        <v>179</v>
+        <v>176</v>
       </c>
       <c r="H3" t="n">
         <v>1.47</v>
@@ -702,7 +702,7 @@
         <v>1.55</v>
       </c>
       <c r="O3" t="n">
-        <v>94552390770</v>
+        <v>94618165920</v>
       </c>
       <c r="P3" t="n">
         <v>4905</v>
@@ -723,7 +723,7 @@
       </c>
       <c r="U3" t="inlineStr"/>
       <c r="V3" t="n">
-        <v>0.3</v>
+        <v>0</v>
       </c>
       <c r="W3" t="inlineStr">
         <is>
@@ -735,7 +735,7 @@
       </c>
       <c r="Y3" t="inlineStr">
         <is>
-          <t>활성</t>
+          <t>추적</t>
         </is>
       </c>
       <c r="Z3" t="inlineStr">
@@ -762,13 +762,13 @@
         <v>0.04</v>
       </c>
       <c r="E4" t="n">
-        <v>74</v>
+        <v>73</v>
       </c>
       <c r="F4" t="n">
-        <v>39</v>
+        <v>40</v>
       </c>
       <c r="G4" t="n">
-        <v>324</v>
+        <v>321</v>
       </c>
       <c r="H4" t="n">
         <v>37.45</v>
@@ -794,7 +794,7 @@
         <v>37.41</v>
       </c>
       <c r="O4" t="n">
-        <v>71919190855</v>
+        <v>71979453175</v>
       </c>
       <c r="P4" t="n">
         <v>19150</v>
@@ -854,13 +854,13 @@
         <v>-0.23</v>
       </c>
       <c r="E5" t="n">
-        <v>107</v>
+        <v>108</v>
       </c>
       <c r="F5" t="n">
         <v>55</v>
       </c>
       <c r="G5" t="n">
-        <v>210</v>
+        <v>213</v>
       </c>
       <c r="H5" t="n">
         <v>4.43</v>
@@ -886,7 +886,7 @@
         <v>4.66</v>
       </c>
       <c r="O5" t="n">
-        <v>59682084940</v>
+        <v>59683828780</v>
       </c>
       <c r="P5" t="n">
         <v>14980</v>
@@ -946,13 +946,13 @@
         <v>-0.8100000000000001</v>
       </c>
       <c r="E6" t="n">
-        <v>134</v>
+        <v>136</v>
       </c>
       <c r="F6" t="n">
-        <v>75</v>
+        <v>77</v>
       </c>
       <c r="G6" t="n">
-        <v>295</v>
+        <v>297</v>
       </c>
       <c r="H6" t="n">
         <v>1.07</v>
@@ -978,7 +978,7 @@
         <v>1.88</v>
       </c>
       <c r="O6" t="n">
-        <v>87909683805</v>
+        <v>87911403835</v>
       </c>
       <c r="P6" t="n">
         <v>22250</v>
@@ -1038,13 +1038,13 @@
         <v>0.08</v>
       </c>
       <c r="E7" t="n">
-        <v>96</v>
+        <v>100</v>
       </c>
       <c r="F7" t="n">
-        <v>65</v>
+        <v>67</v>
       </c>
       <c r="G7" t="n">
-        <v>236</v>
+        <v>246</v>
       </c>
       <c r="H7" t="n">
         <v>31.86</v>
@@ -1070,7 +1070,7 @@
         <v>31.78</v>
       </c>
       <c r="O7" t="n">
-        <v>138058033275</v>
+        <v>138112370775</v>
       </c>
       <c r="P7" t="n">
         <v>45000</v>
@@ -1136,7 +1136,7 @@
         <v>81</v>
       </c>
       <c r="G8" t="n">
-        <v>989</v>
+        <v>1037</v>
       </c>
       <c r="H8" t="n">
         <v>3.47</v>
@@ -1162,7 +1162,7 @@
         <v>4.12</v>
       </c>
       <c r="O8" t="n">
-        <v>62120864750</v>
+        <v>62143753750</v>
       </c>
       <c r="P8" t="n">
         <v>1233000</v>
@@ -1178,7 +1178,7 @@
       </c>
       <c r="T8" t="inlineStr">
         <is>
-          <t>삼천당제약의 연기금 매수세 유입 및 4분기 실적 기대감. '아일리아', '릴레이 계약공시' 등 구체적인 사업 내용 언급과 함께 3연상 기대감 표출. 공매도 금지 조치에 따른 수급 개선 전망.</t>
+          <t>연기금 7일째 매수 및 공매도 과열. 내년 아일리아 영업이익 기대, 릴레이 계약 공시 및 기술 협력 뉴스 언급.</t>
         </is>
       </c>
       <c r="U8" t="inlineStr"/>
@@ -1187,7 +1187,7 @@
       </c>
       <c r="W8" t="inlineStr">
         <is>
-          <t>['아일리아', '계약공시', '공매도']</t>
+          <t>['연기금', '아일리아', '계약 공시']</t>
         </is>
       </c>
       <c r="X8" t="n">
@@ -1222,13 +1222,13 @@
         <v>-0.15</v>
       </c>
       <c r="E9" t="n">
-        <v>693</v>
+        <v>700</v>
       </c>
       <c r="F9" t="n">
         <v>276</v>
       </c>
       <c r="G9" t="n">
-        <v>1718</v>
+        <v>1752</v>
       </c>
       <c r="H9" t="n">
         <v>0.09</v>
@@ -1254,7 +1254,7 @@
         <v>0.24</v>
       </c>
       <c r="O9" t="n">
-        <v>223891791260</v>
+        <v>224025368990</v>
       </c>
       <c r="P9" t="n">
         <v>28700</v>
@@ -1270,16 +1270,16 @@
       </c>
       <c r="T9" t="inlineStr">
         <is>
-          <t>덕산넵코어스 관련 국민권익위 조사 요청 및 사기 상장 의혹 제기.</t>
+          <t>국민권익위 조사 요청 및 금감원 신고 언급. 일부 투자자는 악질 종목이라 칭하며 철저한 조사 촉구.</t>
         </is>
       </c>
       <c r="U9" t="inlineStr"/>
       <c r="V9" t="n">
-        <v>0.3</v>
+        <v>0.2</v>
       </c>
       <c r="W9" t="inlineStr">
         <is>
-          <t>['덕산넵코어스', '사기상장', '국민권익위']</t>
+          <t>['국민권익위', '금감원', '사기상장']</t>
         </is>
       </c>
       <c r="X9" t="n">
@@ -1314,13 +1314,13 @@
         <v>-0.73</v>
       </c>
       <c r="E10" t="n">
-        <v>377</v>
+        <v>380</v>
       </c>
       <c r="F10" t="n">
         <v>193</v>
       </c>
       <c r="G10" t="n">
-        <v>1405</v>
+        <v>1413</v>
       </c>
       <c r="H10" t="n">
         <v>13.39</v>
@@ -1346,7 +1346,7 @@
         <v>14.12</v>
       </c>
       <c r="O10" t="n">
-        <v>41028686975</v>
+        <v>41028732625</v>
       </c>
       <c r="P10" t="n">
         <v>69200</v>
@@ -1362,7 +1362,7 @@
       </c>
       <c r="T10" t="inlineStr">
         <is>
-          <t>HLB의 간암 치료제 관련 기대감 및 FDA 승인 전망. '리보세라닙 병용요법', '무상증자' 등 구체적인 호재 언급과 함께 높은 목표 주가 제시. 공매도 세력에 대한 비판 및 투자자들의 동요 자제 호소.</t>
+          <t>리보세라닙 병용요법 허가 기대감 속 공매도 관련 논쟁. 2026년 연말 30만, FDA 승인 시 90만 기대.</t>
         </is>
       </c>
       <c r="U10" t="inlineStr"/>
@@ -1371,7 +1371,7 @@
       </c>
       <c r="W10" t="inlineStr">
         <is>
-          <t>['리보세라닙', 'FDA', '무상증자']</t>
+          <t>['리보세라닙', '공매도', 'FDA 승인']</t>
         </is>
       </c>
       <c r="X10" t="n">
@@ -1406,13 +1406,13 @@
         <v>-0.31</v>
       </c>
       <c r="E11" t="n">
-        <v>117</v>
+        <v>119</v>
       </c>
       <c r="F11" t="n">
         <v>58</v>
       </c>
       <c r="G11" t="n">
-        <v>249</v>
+        <v>259</v>
       </c>
       <c r="H11" t="n">
         <v>0</v>
@@ -1438,7 +1438,7 @@
         <v>0.31</v>
       </c>
       <c r="O11" t="n">
-        <v>22286162940</v>
+        <v>22287869070</v>
       </c>
       <c r="P11" t="n">
         <v>9680</v>
@@ -1498,13 +1498,13 @@
         <v>-0.17</v>
       </c>
       <c r="E12" t="n">
-        <v>93</v>
+        <v>95</v>
       </c>
       <c r="F12" t="n">
         <v>47</v>
       </c>
       <c r="G12" t="n">
-        <v>300</v>
+        <v>313</v>
       </c>
       <c r="H12" t="n">
         <v>26.38</v>
@@ -1530,7 +1530,7 @@
         <v>26.55</v>
       </c>
       <c r="O12" t="n">
-        <v>24562858195</v>
+        <v>24585183955</v>
       </c>
       <c r="P12" t="n">
         <v>17950</v>
@@ -1593,10 +1593,10 @@
         <v>800</v>
       </c>
       <c r="F13" t="n">
-        <v>543</v>
+        <v>536</v>
       </c>
       <c r="G13" t="n">
-        <v>2520</v>
+        <v>2625</v>
       </c>
       <c r="H13" t="n">
         <v>46.38</v>
@@ -1622,7 +1622,7 @@
         <v>46.37</v>
       </c>
       <c r="O13" t="n">
-        <v>5187816135500</v>
+        <v>5188192629500</v>
       </c>
       <c r="P13" t="n">
         <v>374500</v>
@@ -1638,7 +1638,7 @@
       </c>
       <c r="T13" t="inlineStr">
         <is>
-          <t>삼성전자의 높은 영업이익에도 불구하고 주주환원 정책 미흡 및 국내 증시 전반의 불신 표출. 정치적 이슈와 맞물린 증시 왜곡 및 외인 자금 유출입에 대한 비판.</t>
+          <t>역대급 실적에도 불구하고 주주환원 미흡 지적. 동시호가 장난질 및 국내 증시 전반에 대한 불만 고조.</t>
         </is>
       </c>
       <c r="U13" t="inlineStr"/>
@@ -1647,7 +1647,7 @@
       </c>
       <c r="W13" t="inlineStr">
         <is>
-          <t>['영업이익', '주주환원', '공매도']</t>
+          <t>['영업이익', '주주환원', '동시호가']</t>
         </is>
       </c>
       <c r="X13" t="n">
@@ -1685,10 +1685,10 @@
         <v>800</v>
       </c>
       <c r="F14" t="n">
-        <v>438</v>
+        <v>442</v>
       </c>
       <c r="G14" t="n">
-        <v>1765</v>
+        <v>1905</v>
       </c>
       <c r="H14" t="n">
         <v>49.59</v>
@@ -1714,7 +1714,7 @@
         <v>49.71</v>
       </c>
       <c r="O14" t="n">
-        <v>5182079054000</v>
+        <v>5184155089000</v>
       </c>
       <c r="P14" t="n">
         <v>2987000</v>
@@ -1730,7 +1730,7 @@
       </c>
       <c r="T14" t="inlineStr">
         <is>
-          <t>SK하이닉스의 급격한 주가 하락 및 국내 증시 전반에 대한 불만 표출. 정치적 요인과 맞물린 증시 불안정 및 기관·외인의 의도적인 주가 조작 의혹 제기.</t>
+          <t>자사주 매입 의결 후 주가 제자리걸음. 현 정부 및 증시 시스템에 대한 불만 표출.</t>
         </is>
       </c>
       <c r="U14" t="inlineStr"/>
@@ -1739,7 +1739,7 @@
       </c>
       <c r="W14" t="inlineStr">
         <is>
-          <t>['주가', '증시', '공매도']</t>
+          <t>['자사주 매입', '주가', '증시 시스템']</t>
         </is>
       </c>
       <c r="X14" t="n">
@@ -1774,13 +1774,13 @@
         <v>-0.1</v>
       </c>
       <c r="E15" t="n">
-        <v>493</v>
+        <v>531</v>
       </c>
       <c r="F15" t="n">
-        <v>289</v>
+        <v>306</v>
       </c>
       <c r="G15" t="n">
-        <v>1553</v>
+        <v>1621</v>
       </c>
       <c r="H15" t="n">
         <v>22.49</v>
@@ -1806,7 +1806,7 @@
         <v>22.59</v>
       </c>
       <c r="O15" t="n">
-        <v>328718171450</v>
+        <v>330473561450</v>
       </c>
       <c r="P15" t="n">
         <v>139200</v>
@@ -1866,13 +1866,13 @@
         <v>0.01</v>
       </c>
       <c r="E16" t="n">
-        <v>155</v>
+        <v>159</v>
       </c>
       <c r="F16" t="n">
         <v>84</v>
       </c>
       <c r="G16" t="n">
-        <v>453</v>
+        <v>455</v>
       </c>
       <c r="H16" t="n">
         <v>27.68</v>
@@ -1898,7 +1898,7 @@
         <v>27.67</v>
       </c>
       <c r="O16" t="n">
-        <v>67113974970</v>
+        <v>67120575970</v>
       </c>
       <c r="P16" t="n">
         <v>35350</v>
@@ -1958,13 +1958,13 @@
         <v>1.19</v>
       </c>
       <c r="E17" t="n">
-        <v>145</v>
+        <v>146</v>
       </c>
       <c r="F17" t="n">
-        <v>92</v>
+        <v>93</v>
       </c>
       <c r="G17" t="n">
-        <v>220</v>
+        <v>224</v>
       </c>
       <c r="H17" t="n">
         <v>4.46</v>
@@ -1990,7 +1990,7 @@
         <v>3.27</v>
       </c>
       <c r="O17" t="n">
-        <v>93837806846</v>
+        <v>93841999986</v>
       </c>
       <c r="P17" t="n">
         <v>5470</v>
@@ -2006,16 +2006,16 @@
       </c>
       <c r="T17" t="inlineStr">
         <is>
-          <t>미국 항생제 보유 회사 주가 급등 및 WHO의 러시아 폐렴 관련 불확실성 속 국제 약품 관련 기대감 표출. 다만, 사망자 수 관련 상반된 보도 및 국제 정세 불안으로 인한 투자 심리 위축 우려.</t>
+          <t>미국 항생제 회사 주가 폭등, WHO 러시아 폐렴 관련 정보 파악 못해. 국제 분위기 불안정 속에 일부 투자자 상한가 기대.</t>
         </is>
       </c>
       <c r="U17" t="inlineStr"/>
       <c r="V17" t="n">
-        <v>0.1</v>
+        <v>0.3</v>
       </c>
       <c r="W17" t="inlineStr">
         <is>
-          <t>['항생제', '전염병', '국제']</t>
+          <t>['항생제', '폐렴', '국제 분위기']</t>
         </is>
       </c>
       <c r="X17" t="n">
@@ -2050,13 +2050,13 @@
         <v>-0.04</v>
       </c>
       <c r="E18" t="n">
-        <v>137</v>
+        <v>145</v>
       </c>
       <c r="F18" t="n">
-        <v>60</v>
+        <v>61</v>
       </c>
       <c r="G18" t="n">
-        <v>719</v>
+        <v>728</v>
       </c>
       <c r="H18" t="n">
         <v>9.460000000000001</v>
@@ -2082,7 +2082,7 @@
         <v>9.5</v>
       </c>
       <c r="O18" t="n">
-        <v>57542446855</v>
+        <v>57572319495</v>
       </c>
       <c r="P18" t="n">
         <v>40350</v>
@@ -2142,13 +2142,13 @@
         <v>-0.95</v>
       </c>
       <c r="E19" t="n">
-        <v>153</v>
+        <v>151</v>
       </c>
       <c r="F19" t="n">
-        <v>90</v>
+        <v>88</v>
       </c>
       <c r="G19" t="n">
-        <v>610</v>
+        <v>612</v>
       </c>
       <c r="H19" t="n">
         <v>3.97</v>
@@ -2174,7 +2174,7 @@
         <v>4.92</v>
       </c>
       <c r="O19" t="n">
-        <v>104127279070</v>
+        <v>104189558970</v>
       </c>
       <c r="P19" t="n">
         <v>31500</v>
@@ -2234,13 +2234,13 @@
         <v>0.02</v>
       </c>
       <c r="E20" t="n">
-        <v>363</v>
+        <v>369</v>
       </c>
       <c r="F20" t="n">
-        <v>166</v>
+        <v>169</v>
       </c>
       <c r="G20" t="n">
-        <v>810</v>
+        <v>808</v>
       </c>
       <c r="H20" t="n">
         <v>1.32</v>
@@ -2266,7 +2266,7 @@
         <v>1.3</v>
       </c>
       <c r="O20" t="n">
-        <v>64488721150</v>
+        <v>64563220450</v>
       </c>
       <c r="P20" t="n">
         <v>63800</v>
@@ -2326,13 +2326,13 @@
         <v>-0.76</v>
       </c>
       <c r="E21" t="n">
-        <v>82</v>
+        <v>88</v>
       </c>
       <c r="F21" t="n">
-        <v>57</v>
+        <v>59</v>
       </c>
       <c r="G21" t="n">
-        <v>227</v>
+        <v>229</v>
       </c>
       <c r="H21" t="n">
         <v>10.02</v>
@@ -2358,7 +2358,7 @@
         <v>10.78</v>
       </c>
       <c r="O21" t="n">
-        <v>77461483400</v>
+        <v>77518048700</v>
       </c>
       <c r="P21" t="n">
         <v>75900</v>
@@ -2424,7 +2424,7 @@
         <v>63</v>
       </c>
       <c r="G22" t="n">
-        <v>367</v>
+        <v>369</v>
       </c>
       <c r="H22" t="n">
         <v>4.65</v>
@@ -2450,7 +2450,7 @@
         <v>4.72</v>
       </c>
       <c r="O22" t="n">
-        <v>73705496350</v>
+        <v>73774421460</v>
       </c>
       <c r="P22" t="n">
         <v>8100</v>
@@ -2542,7 +2542,7 @@
         <v>2.37</v>
       </c>
       <c r="O23" t="n">
-        <v>37860696300</v>
+        <v>38864216640</v>
       </c>
       <c r="P23" t="n">
         <v>17590</v>
@@ -2602,13 +2602,13 @@
         <v>-2.03</v>
       </c>
       <c r="E24" t="n">
-        <v>249</v>
+        <v>251</v>
       </c>
       <c r="F24" t="n">
-        <v>107</v>
+        <v>108</v>
       </c>
       <c r="G24" t="n">
-        <v>709</v>
+        <v>719</v>
       </c>
       <c r="H24" t="n">
         <v>3.09</v>
@@ -2634,7 +2634,7 @@
         <v>5.12</v>
       </c>
       <c r="O24" t="n">
-        <v>98641227755</v>
+        <v>98661929675</v>
       </c>
       <c r="P24" t="n">
         <v>23500</v>
@@ -2694,13 +2694,13 @@
         <v>0.03</v>
       </c>
       <c r="E25" t="n">
-        <v>127</v>
+        <v>129</v>
       </c>
       <c r="F25" t="n">
-        <v>66</v>
+        <v>68</v>
       </c>
       <c r="G25" t="n">
-        <v>399</v>
+        <v>403</v>
       </c>
       <c r="H25" t="n">
         <v>5.04</v>
@@ -2726,7 +2726,7 @@
         <v>5.01</v>
       </c>
       <c r="O25" t="n">
-        <v>7843307780</v>
+        <v>7843317560</v>
       </c>
       <c r="P25" t="n">
         <v>15900</v>
@@ -2742,16 +2742,16 @@
       </c>
       <c r="T25" t="inlineStr">
         <is>
-          <t>신풍제약 관련 바이러스 테마주로서의 기대감 형성. 자사주 매집 물량 언급 및 상승 가능성 제시. 일부 매도세에 대한 경계.</t>
+          <t>케냐 에볼라 확진 및 러시아 관련 부정적 전망. 일부 투자자는 자사주 매집 물량 언급하며 버티기 호소, 20만 목표 제시.</t>
         </is>
       </c>
       <c r="U25" t="inlineStr"/>
       <c r="V25" t="n">
-        <v>0.2</v>
+        <v>0.3</v>
       </c>
       <c r="W25" t="inlineStr">
         <is>
-          <t>['바이러스', '자사주', '테마주']</t>
+          <t>['에볼라', '자사주 매집', '목표가']</t>
         </is>
       </c>
       <c r="X25" t="n">
